--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A23742C-8ADF-411E-B438-9ABF8BE0E1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54577C2F-7886-4A1E-AD54-B6F937AD03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="258" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5363" uniqueCount="2301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5367" uniqueCount="2306">
   <si>
     <t>https://www.pornhub.com/view_video.php?viewkey=ph5db33702d8ca6</t>
   </si>
@@ -6783,9 +6783,6 @@
     <t>teen,fingering,butt plug,spank,anal</t>
   </si>
   <si>
-    <t>1f-1f,fist,sybian</t>
-  </si>
-  <si>
     <t>nipple suction at 1m,spike wheel at 5m,wax at 10m</t>
   </si>
   <si>
@@ -6964,6 +6961,24 @@
   </si>
   <si>
     <t>tit pull at 3m,spank at 15m,closeup pussy at 15m,much normal except the closeups of the white pussy</t>
+  </si>
+  <si>
+    <t>pretzel,aufd hands front,split suspended</t>
+  </si>
+  <si>
+    <t>1f-1f,tape gag,pussy clamps,nipple clamps,anal hook,cane,flog,electric,fist,ball gag,sybian</t>
+  </si>
+  <si>
+    <t>very creative positions and all the hardcore equipment</t>
+  </si>
+  <si>
+    <t>sit,inverted pussy over face extreme,suspended face down horizontal</t>
+  </si>
+  <si>
+    <t>nipple suction at 17m,spank at 22m,nipple pull at 37m,nipple mouse traps at 37m</t>
+  </si>
+  <si>
+    <t>tit bound,rope gag,whip,flog,cane,anal hook,nipple suction,spank,oiled,nipple pull,nipple mouse traps,sybian</t>
   </si>
 </sst>
 </file>
@@ -9096,7 +9111,7 @@
         <v>52</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>2167</v>
@@ -9162,10 +9177,10 @@
         <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>49</v>
@@ -9174,7 +9189,7 @@
         <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="L28" s="1" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.REGEXEXTRACT(B28,"(?&lt;=//)[^/]+")</f>
@@ -9213,7 +9228,7 @@
         <v>Done</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C29" s="1">
         <v>52</v>
@@ -9228,10 +9243,10 @@
         <v>53</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>49</v>
@@ -9240,7 +9255,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="L29" s="1" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.REGEXEXTRACT(B29,"(?&lt;=//)[^/]+")</f>
@@ -11340,7 +11355,7 @@
         <v>52</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>2210</v>
@@ -11406,7 +11421,7 @@
         <v>53</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>2069</v>
@@ -11418,7 +11433,7 @@
         <v>7</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="L62" s="1" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.REGEXEXTRACT(B62,"(?&lt;=//)[^/]+")</f>
@@ -11472,7 +11487,7 @@
         <v>53</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>74</v>
@@ -11484,7 +11499,7 @@
         <v>7</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="L63" s="1" t="str" cm="1">
         <f t="array" ref="L63">_xlfn.REGEXEXTRACT(B63,"(?&lt;=//)[^/]+")</f>
@@ -11934,7 +11949,7 @@
         <v>127</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>317</v>
@@ -14112,7 +14127,7 @@
         <v>53</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>2080</v>
@@ -16752,7 +16767,7 @@
         <v>53</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>793</v>
@@ -16764,7 +16779,7 @@
         <v>5</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="L143" s="1" t="str" cm="1">
         <f t="array" ref="L143">_xlfn.REGEXEXTRACT(B143,"(?&lt;=//)[^/]+")</f>
@@ -16884,7 +16899,7 @@
         <v>127</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>2148</v>
@@ -17346,7 +17361,7 @@
         <v>127</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>324</v>
@@ -18468,7 +18483,7 @@
         <v>53</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>2067</v>
@@ -19260,10 +19275,10 @@
         <v>53</v>
       </c>
       <c r="G181" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="H181" s="1" t="s">
         <v>2248</v>
-      </c>
-      <c r="H181" s="1" t="s">
-        <v>2249</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>49</v>
@@ -19272,7 +19287,7 @@
         <v>4</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="L181" s="1" t="str" cm="1">
         <f t="array" ref="L181">_xlfn.REGEXEXTRACT(B181,"(?&lt;=//)[^/]+")</f>
@@ -19326,7 +19341,7 @@
         <v>53</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>2065</v>
@@ -19338,7 +19353,7 @@
         <v>4</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="L182" s="1" t="str" cm="1">
         <f t="array" ref="L182">_xlfn.REGEXEXTRACT(B182,"(?&lt;=//)[^/]+")</f>
@@ -19524,7 +19539,7 @@
         <v>127</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>2131</v>
@@ -19590,7 +19605,7 @@
         <v>127</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>2108</v>
@@ -21291,7 +21306,7 @@
         <v>Done</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="C212" s="1">
         <v>19</v>
@@ -21306,10 +21321,10 @@
         <v>53</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>49</v>
@@ -21318,7 +21333,7 @@
         <v>3</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="L212" s="1" t="str" cm="1">
         <f t="array" ref="L212">_xlfn.REGEXEXTRACT(B212,"(?&lt;=//)[^/]+")</f>
@@ -21345,7 +21360,7 @@
         <v>1541</v>
       </c>
       <c r="S212" s="1" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="T212" s="1">
         <v>0</v>
@@ -21372,10 +21387,10 @@
         <v>53</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>49</v>
@@ -21384,7 +21399,7 @@
         <v>3</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="L213" s="1" t="str" cm="1">
         <f t="array" ref="L213">_xlfn.REGEXEXTRACT(B213,"(?&lt;=//)[^/]+")</f>
@@ -21438,7 +21453,7 @@
         <v>54</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>2065</v>
@@ -21450,7 +21465,7 @@
         <v>3</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="L214" s="1" t="str" cm="1">
         <f t="array" ref="L214">_xlfn.REGEXEXTRACT(B214,"(?&lt;=//)[^/]+")</f>
@@ -22032,7 +22047,7 @@
         <v>53</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>835</v>
@@ -22044,7 +22059,7 @@
         <v>2</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="L223" s="1" t="str" cm="1">
         <f t="array" ref="L223">_xlfn.REGEXEXTRACT(B223,"(?&lt;=//)[^/]+")</f>
@@ -22098,7 +22113,7 @@
         <v>1877</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>2133</v>
@@ -22296,10 +22311,10 @@
         <v>53</v>
       </c>
       <c r="G227" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="H227" s="1" t="s">
         <v>2269</v>
-      </c>
-      <c r="H227" s="1" t="s">
-        <v>2270</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>49</v>
@@ -22308,7 +22323,7 @@
         <v>1</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="L227" s="1" t="str" cm="1">
         <f t="array" ref="L227">_xlfn.REGEXEXTRACT(B227,"(?&lt;=//)[^/]+")</f>
@@ -22362,7 +22377,7 @@
         <v>54</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>55</v>
@@ -22374,7 +22389,7 @@
         <v>1</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="L228" s="1" t="str" cm="1">
         <f t="array" ref="L228">_xlfn.REGEXEXTRACT(B228,"(?&lt;=//)[^/]+")</f>
@@ -22658,10 +22673,10 @@
         <v>53</v>
       </c>
       <c r="G233" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="H233" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="H233" s="1" t="s">
-        <v>2291</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>49</v>
@@ -22670,7 +22685,7 @@
         <v>5</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="L233" s="1" t="str" cm="1">
         <f t="array" ref="L233">_xlfn.REGEXEXTRACT(B233,"(?&lt;=//)[^/]+")</f>
@@ -23306,7 +23321,7 @@
         <v>53</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -24118,7 +24133,7 @@
         <v>53</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="H258" s="1" t="s">
         <v>2137</v>
@@ -25100,7 +25115,7 @@
         <v>53</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="H275" s="1"/>
       <c r="I275" s="1"/>
@@ -26030,7 +26045,7 @@
         <v>53</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="H291" s="1"/>
       <c r="I291" s="1"/>
@@ -27712,10 +27727,10 @@
         <v>53</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>49</v>
@@ -27724,7 +27739,7 @@
         <v>8</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="L320" s="1" t="str" cm="1">
         <f t="array" ref="L320">_xlfn.REGEXEXTRACT(B320,"(?&lt;=//)[^/]+")</f>
@@ -27778,10 +27793,10 @@
         <v>54</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>49</v>
@@ -27790,7 +27805,7 @@
         <v>7</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="L321" s="1" t="str" cm="1">
         <f t="array" ref="L321">_xlfn.REGEXEXTRACT(B321,"(?&lt;=//)[^/]+")</f>
@@ -28534,10 +28549,10 @@
         <v>53</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>49</v>
@@ -28546,7 +28561,7 @@
         <v>6</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="L334" s="1" t="str" cm="1">
         <f t="array" ref="L334">_xlfn.REGEXEXTRACT(B334,"(?&lt;=//)[^/]+")</f>
@@ -29103,10 +29118,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>932</v>
@@ -29124,14 +29139,20 @@
         <v>54</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>2240</v>
+        <v>2301</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I344" s="1"/>
-      <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
+        <v>2300</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J344" s="1">
+        <v>8</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>2302</v>
+      </c>
       <c r="L344" s="1" t="str" cm="1">
         <f t="array" ref="L344">_xlfn.REGEXEXTRACT(B344,"(?&lt;=//)[^/]+")</f>
         <v>hcbdsm.com</v>
@@ -29221,10 +29242,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>Pending</v>
+        <v>Done</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>977</v>
@@ -29242,14 +29263,20 @@
         <v>53</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>922</v>
+        <v>2305</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="I346" s="1"/>
-      <c r="J346" s="1"/>
-      <c r="K346" s="1"/>
+        <v>2303</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J346" s="1">
+        <v>8</v>
+      </c>
+      <c r="K346" s="1" t="s">
+        <v>2304</v>
+      </c>
       <c r="L346" s="1" t="str" cm="1">
         <f t="array" ref="L346">_xlfn.REGEXEXTRACT(B346,"(?&lt;=//)[^/]+")</f>
         <v>hcbdsm.com</v>
@@ -32654,7 +32681,7 @@
         <v>53</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="H405" s="1"/>
       <c r="I405" s="1"/>

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54577C2F-7886-4A1E-AD54-B6F937AD03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4214E119-FC9E-4173-B124-BB7C5B4C518F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="258" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5367" uniqueCount="2306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="2309">
   <si>
     <t>https://www.pornhub.com/view_video.php?viewkey=ph5db33702d8ca6</t>
   </si>
@@ -5631,9 +5631,6 @@
     <t>pussy hose,wax ass,oiled,anal hook</t>
   </si>
   <si>
-    <t>oiled,nipple clamps</t>
-  </si>
-  <si>
     <t>oiled,anal hook</t>
   </si>
   <si>
@@ -5658,9 +5655,6 @@
     <t>pretzel extreme</t>
   </si>
   <si>
-    <t>live,oiled,og,nipple clamps</t>
-  </si>
-  <si>
     <t>2f-1m,outdoor</t>
   </si>
   <si>
@@ -6979,6 +6973,21 @@
   </si>
   <si>
     <t>tit bound,rope gag,whip,flog,cane,anal hook,nipple suction,spank,oiled,nipple pull,nipple mouse traps,sybian</t>
+  </si>
+  <si>
+    <t>panty gag at 1m,nipple clamps at 16m,oiled at 20m</t>
+  </si>
+  <si>
+    <t>arched n,missionary</t>
+  </si>
+  <si>
+    <t>armpits,panty gag,flog,vibrator,nipple clamps,blindfold,oiled</t>
+  </si>
+  <si>
+    <t>pussy flog at 10m,spank at 29m,oiled at 41m,stick in nipple clamps at 44m</t>
+  </si>
+  <si>
+    <t>live,oiled,og,nipple clamps,flog,bite gag,pussy flog,pussy clamps,spank,vibrator</t>
   </si>
 </sst>
 </file>
@@ -7461,7 +7470,7 @@
         <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>602</v>
@@ -7500,7 +7509,7 @@
         <v>551</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="T2" s="1">
         <v>0</v>
@@ -7527,10 +7536,10 @@
         <v>53</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>49</v>
@@ -7578,7 +7587,7 @@
         <v>Done</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C4" s="1">
         <v>77</v>
@@ -7593,7 +7602,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>61</v>
@@ -7662,7 +7671,7 @@
         <v>481</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>49</v>
@@ -7719,16 +7728,16 @@
         <v>627</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>49</v>
@@ -7737,7 +7746,7 @@
         <v>10</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="L6" s="1" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.REGEXEXTRACT(B6,"(?&lt;=//)[^/]+")</f>
@@ -7794,7 +7803,7 @@
         <v>873</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>49</v>
@@ -7992,7 +8001,7 @@
         <v>300</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>49</v>
@@ -8058,7 +8067,7 @@
         <v>503</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>49</v>
@@ -8124,7 +8133,7 @@
         <v>541</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>49</v>
@@ -8187,7 +8196,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>695</v>
@@ -8322,7 +8331,7 @@
         <v>584</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>49</v>
@@ -8355,10 +8364,10 @@
         <v>0</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="T15" s="1">
         <v>0</v>
@@ -8388,7 +8397,7 @@
         <v>298</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>49</v>
@@ -8397,7 +8406,7 @@
         <v>8</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="L16" s="1" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.REGEXEXTRACT(B16,"(?&lt;=//)[^/]+")</f>
@@ -8451,10 +8460,10 @@
         <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>49</v>
@@ -8520,7 +8529,7 @@
         <v>361</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>49</v>
@@ -8586,7 +8595,7 @@
         <v>903</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>49</v>
@@ -8649,7 +8658,7 @@
         <v>129</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>61</v>
@@ -8661,7 +8670,7 @@
         <v>8</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="L20" s="1" t="str" cm="1">
         <f t="array" ref="L20">_xlfn.REGEXEXTRACT(B20,"(?&lt;=//)[^/]+")</f>
@@ -8718,7 +8727,7 @@
         <v>600</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>49</v>
@@ -8727,7 +8736,7 @@
         <v>8</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="L21" s="1" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.REGEXEXTRACT(B21,"(?&lt;=//)[^/]+")</f>
@@ -8781,10 +8790,10 @@
         <v>53</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>49</v>
@@ -8850,7 +8859,7 @@
         <v>381</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>49</v>
@@ -8916,7 +8925,7 @@
         <v>386</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>49</v>
@@ -8949,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>1412</v>
@@ -8973,7 +8982,7 @@
         <v>625</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>54</v>
@@ -9111,10 +9120,10 @@
         <v>52</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>49</v>
@@ -9147,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>1347</v>
@@ -9177,10 +9186,10 @@
         <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>49</v>
@@ -9189,7 +9198,7 @@
         <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="L28" s="1" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.REGEXEXTRACT(B28,"(?&lt;=//)[^/]+")</f>
@@ -9228,7 +9237,7 @@
         <v>Done</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C29" s="1">
         <v>52</v>
@@ -9243,10 +9252,10 @@
         <v>53</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>49</v>
@@ -9255,7 +9264,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="L29" s="1" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.REGEXEXTRACT(B29,"(?&lt;=//)[^/]+")</f>
@@ -9387,7 +9396,7 @@
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="L31" s="1" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.REGEXEXTRACT(B31,"(?&lt;=//)[^/]+")</f>
@@ -9441,7 +9450,7 @@
         <v>63</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>311</v>
@@ -9573,10 +9582,10 @@
         <v>53</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>49</v>
@@ -9708,7 +9717,7 @@
         <v>363</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>49</v>
@@ -9774,7 +9783,7 @@
         <v>887</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>49</v>
@@ -9837,10 +9846,10 @@
         <v>157</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>49</v>
@@ -9906,7 +9915,7 @@
         <v>437</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>49</v>
@@ -9942,7 +9951,7 @@
         <v>1298</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="T39" s="1">
         <v>0</v>
@@ -9969,7 +9978,7 @@
         <v>63</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>463</v>
@@ -10038,7 +10047,7 @@
         <v>377</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>49</v>
@@ -10047,7 +10056,7 @@
         <v>7</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="L41" s="1" t="str" cm="1">
         <f t="array" ref="L41">_xlfn.REGEXEXTRACT(B41,"(?&lt;=//)[^/]+")</f>
@@ -10101,10 +10110,10 @@
         <v>54</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>49</v>
@@ -10170,7 +10179,7 @@
         <v>1420</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>49</v>
@@ -10233,10 +10242,10 @@
         <v>53</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>49</v>
@@ -10299,10 +10308,10 @@
         <v>54</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>49</v>
@@ -10338,7 +10347,7 @@
         <v>1288</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="T45" s="1">
         <v>0</v>
@@ -10365,10 +10374,10 @@
         <v>54</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>49</v>
@@ -10404,7 +10413,7 @@
         <v>1321</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="T46" s="1">
         <v>0</v>
@@ -10425,13 +10434,13 @@
         <v>907</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>473</v>
@@ -10443,7 +10452,7 @@
         <v>7</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="L47" s="1" t="str" cm="1">
         <f t="array" ref="L47">_xlfn.REGEXEXTRACT(B47,"(?&lt;=//)[^/]+")</f>
@@ -10497,10 +10506,10 @@
         <v>53</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>49</v>
@@ -10695,7 +10704,7 @@
         <v>63</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>328</v>
@@ -10707,7 +10716,7 @@
         <v>7</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="L51" s="1" t="str" cm="1">
         <f t="array" ref="L51">_xlfn.REGEXEXTRACT(B51,"(?&lt;=//)[^/]+")</f>
@@ -10893,7 +10902,7 @@
         <v>53</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>61</v>
@@ -10959,10 +10968,10 @@
         <v>54</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>49</v>
@@ -10971,7 +10980,7 @@
         <v>7</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="L55" s="1" t="str" cm="1">
         <f t="array" ref="L55">_xlfn.REGEXEXTRACT(B55,"(?&lt;=//)[^/]+")</f>
@@ -10998,7 +11007,7 @@
         <v>1297</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="T55" s="1">
         <v>0</v>
@@ -11025,10 +11034,10 @@
         <v>53</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>49</v>
@@ -11091,10 +11100,10 @@
         <v>53</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>49</v>
@@ -11127,10 +11136,10 @@
         <v>1</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="T57" s="1">
         <v>0</v>
@@ -11157,10 +11166,10 @@
         <v>53</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>49</v>
@@ -11169,7 +11178,7 @@
         <v>7</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="L58" s="1" t="str" cm="1">
         <f t="array" ref="L58">_xlfn.REGEXEXTRACT(B58,"(?&lt;=//)[^/]+")</f>
@@ -11262,7 +11271,7 @@
         <v>1301</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="T59" s="1">
         <v>0</v>
@@ -11292,7 +11301,7 @@
         <v>677</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>49</v>
@@ -11355,10 +11364,10 @@
         <v>52</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>49</v>
@@ -11367,7 +11376,7 @@
         <v>7</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="L61" s="1" t="str" cm="1">
         <f t="array" ref="L61">_xlfn.REGEXEXTRACT(B61,"(?&lt;=//)[^/]+")</f>
@@ -11421,10 +11430,10 @@
         <v>53</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>49</v>
@@ -11433,7 +11442,7 @@
         <v>7</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="L62" s="1" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.REGEXEXTRACT(B62,"(?&lt;=//)[^/]+")</f>
@@ -11457,10 +11466,10 @@
         <v>0</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="T62" s="1">
         <v>0</v>
@@ -11487,7 +11496,7 @@
         <v>53</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>74</v>
@@ -11499,7 +11508,7 @@
         <v>7</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="L63" s="1" t="str" cm="1">
         <f t="array" ref="L63">_xlfn.REGEXEXTRACT(B63,"(?&lt;=//)[^/]+")</f>
@@ -11523,10 +11532,10 @@
         <v>0</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="T63" s="1">
         <v>8</v>
@@ -11553,10 +11562,10 @@
         <v>53</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>49</v>
@@ -11619,10 +11628,10 @@
         <v>53</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>49</v>
@@ -11688,7 +11697,7 @@
         <v>415</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>49</v>
@@ -11817,7 +11826,7 @@
         <v>53</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>454</v>
@@ -11883,10 +11892,10 @@
         <v>63</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>49</v>
@@ -11949,7 +11958,7 @@
         <v>127</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>317</v>
@@ -12018,7 +12027,7 @@
         <v>445</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>49</v>
@@ -12084,7 +12093,7 @@
         <v>418</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>49</v>
@@ -12216,7 +12225,7 @@
         <v>411</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>49</v>
@@ -12273,7 +12282,7 @@
         <v>627</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>53</v>
@@ -12282,7 +12291,7 @@
         <v>1821</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>49</v>
@@ -12489,7 +12498,7 @@
         <v>6</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="L78" s="1" t="str" cm="1">
         <f t="array" ref="L78">_xlfn.REGEXEXTRACT(B78,"(?&lt;=//)[^/]+")</f>
@@ -12546,7 +12555,7 @@
         <v>1820</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>49</v>
@@ -12555,7 +12564,7 @@
         <v>6</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="L79" s="1" t="str" cm="1">
         <f t="array" ref="L79">_xlfn.REGEXEXTRACT(B79,"(?&lt;=//)[^/]+")</f>
@@ -12675,7 +12684,7 @@
         <v>54</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>328</v>
@@ -12741,7 +12750,7 @@
         <v>53</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>332</v>
@@ -12933,7 +12942,7 @@
         <v>907</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>53</v>
@@ -13074,7 +13083,7 @@
         <v>382</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>49</v>
@@ -13083,7 +13092,7 @@
         <v>6</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="L87" s="1" t="str" cm="1">
         <f t="array" ref="L87">_xlfn.REGEXEXTRACT(B87,"(?&lt;=//)[^/]+")</f>
@@ -13203,7 +13212,7 @@
         <v>53</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>509</v>
@@ -13305,10 +13314,10 @@
         <v>0</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="S90" s="1" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="T90" s="1">
         <v>0</v>
@@ -13338,7 +13347,7 @@
         <v>517</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>49</v>
@@ -13404,7 +13413,7 @@
         <v>362</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>49</v>
@@ -13545,7 +13554,7 @@
         <v>6</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="L94" s="1" t="str" cm="1">
         <f t="array" ref="L94">_xlfn.REGEXEXTRACT(B94,"(?&lt;=//)[^/]+")</f>
@@ -13809,7 +13818,7 @@
         <v>6</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="L98" s="1" t="str" cm="1">
         <f t="array" ref="L98">_xlfn.REGEXEXTRACT(B98,"(?&lt;=//)[^/]+")</f>
@@ -13863,10 +13872,10 @@
         <v>54</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>49</v>
@@ -13875,7 +13884,7 @@
         <v>6</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="L99" s="1" t="str" cm="1">
         <f t="array" ref="L99">_xlfn.REGEXEXTRACT(B99,"(?&lt;=//)[^/]+")</f>
@@ -13899,7 +13908,7 @@
         <v>1</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="S99" s="1" t="s">
         <v>1335</v>
@@ -13932,7 +13941,7 @@
         <v>720</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>49</v>
@@ -13998,7 +14007,7 @@
         <v>412</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>49</v>
@@ -14127,10 +14136,10 @@
         <v>53</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>49</v>
@@ -14139,7 +14148,7 @@
         <v>6</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="L103" s="1" t="str" cm="1">
         <f t="array" ref="L103">_xlfn.REGEXEXTRACT(B103,"(?&lt;=//)[^/]+")</f>
@@ -14193,10 +14202,10 @@
         <v>63</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>49</v>
@@ -14205,7 +14214,7 @@
         <v>6</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="L104" s="1" t="str" cm="1">
         <f t="array" ref="L104">_xlfn.REGEXEXTRACT(B104,"(?&lt;=//)[^/]+")</f>
@@ -14259,7 +14268,7 @@
         <v>63</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>321</v>
@@ -14328,7 +14337,7 @@
         <v>1819</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>49</v>
@@ -14655,7 +14664,7 @@
         <v>63</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>468</v>
@@ -14667,7 +14676,7 @@
         <v>5</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="L111" s="1" t="str" cm="1">
         <f t="array" ref="L111">_xlfn.REGEXEXTRACT(B111,"(?&lt;=//)[^/]+")</f>
@@ -14724,7 +14733,7 @@
         <v>883</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>49</v>
@@ -14856,7 +14865,7 @@
         <v>1210</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>49</v>
@@ -14865,7 +14874,7 @@
         <v>5</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="L114" s="1" t="str" cm="1">
         <f t="array" ref="L114">_xlfn.REGEXEXTRACT(B114,"(?&lt;=//)[^/]+")</f>
@@ -14913,7 +14922,7 @@
         <v>627</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>53</v>
@@ -14955,10 +14964,10 @@
         <v>1</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="T115" s="1">
         <v>0</v>
@@ -15054,7 +15063,7 @@
         <v>396</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>49</v>
@@ -15120,7 +15129,7 @@
         <v>1226</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>49</v>
@@ -15153,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="T118" s="1">
         <v>0</v>
@@ -15183,7 +15192,7 @@
         <v>53</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>472</v>
@@ -15318,7 +15327,7 @@
         <v>395</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>49</v>
@@ -15381,7 +15390,7 @@
         <v>54</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>464</v>
@@ -15579,10 +15588,10 @@
         <v>157</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>247</v>
@@ -15645,10 +15654,10 @@
         <v>54</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>49</v>
@@ -15780,7 +15789,7 @@
         <v>367</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>49</v>
@@ -15846,7 +15855,7 @@
         <v>358</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>49</v>
@@ -15855,7 +15864,7 @@
         <v>5</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="L129" s="1" t="str" cm="1">
         <f t="array" ref="L129">_xlfn.REGEXEXTRACT(B129,"(?&lt;=//)[^/]+")</f>
@@ -15909,7 +15918,7 @@
         <v>129</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>319</v>
@@ -15921,7 +15930,7 @@
         <v>5</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="L130" s="1" t="str" cm="1">
         <f t="array" ref="L130">_xlfn.REGEXEXTRACT(B130,"(?&lt;=//)[^/]+")</f>
@@ -15960,7 +15969,7 @@
         <v>Done</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="C131" s="1">
         <v>11</v>
@@ -15987,7 +15996,7 @@
         <v>5</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="L131" s="1" t="str" cm="1">
         <f t="array" ref="L131">_xlfn.REGEXEXTRACT(B131,"(?&lt;=//)[^/]+")</f>
@@ -16026,7 +16035,7 @@
         <v>Done</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="C132" s="1">
         <v>12</v>
@@ -16110,7 +16119,7 @@
         <v>417</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>49</v>
@@ -16143,10 +16152,10 @@
         <v>0</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="S133" s="1" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="T133" s="1">
         <v>0</v>
@@ -16173,10 +16182,10 @@
         <v>53</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>49</v>
@@ -16239,10 +16248,10 @@
         <v>53</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>49</v>
@@ -16308,7 +16317,7 @@
         <v>399</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>49</v>
@@ -16440,7 +16449,7 @@
         <v>426</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>49</v>
@@ -16473,10 +16482,10 @@
         <v>0</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="S138" s="1" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="T138" s="1">
         <v>0</v>
@@ -16506,7 +16515,7 @@
         <v>898</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>49</v>
@@ -16620,7 +16629,7 @@
         <v>Done</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C141" s="1">
         <v>129</v>
@@ -16629,7 +16638,7 @@
         <v>907</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>53</v>
@@ -16704,7 +16713,7 @@
         <v>582</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>49</v>
@@ -16767,7 +16776,7 @@
         <v>53</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>793</v>
@@ -16779,7 +16788,7 @@
         <v>5</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="L143" s="1" t="str" cm="1">
         <f t="array" ref="L143">_xlfn.REGEXEXTRACT(B143,"(?&lt;=//)[^/]+")</f>
@@ -16803,10 +16812,10 @@
         <v>0</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="S143" s="1" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="T143" s="1">
         <v>8</v>
@@ -16833,10 +16842,10 @@
         <v>63</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>207</v>
@@ -16899,10 +16908,10 @@
         <v>127</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>49</v>
@@ -16911,7 +16920,7 @@
         <v>4</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="L145" s="1" t="str" cm="1">
         <f t="array" ref="L145">_xlfn.REGEXEXTRACT(B145,"(?&lt;=//)[^/]+")</f>
@@ -16968,7 +16977,7 @@
         <v>390</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>49</v>
@@ -17034,7 +17043,7 @@
         <v>436</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>49</v>
@@ -17097,10 +17106,10 @@
         <v>54</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>49</v>
@@ -17166,7 +17175,7 @@
         <v>385</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>49</v>
@@ -17214,7 +17223,7 @@
         <v>Done</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="C150" s="1">
         <v>37</v>
@@ -17229,10 +17238,10 @@
         <v>127</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>49</v>
@@ -17241,7 +17250,7 @@
         <v>4</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="L150" s="1" t="str" cm="1">
         <f t="array" ref="L150">_xlfn.REGEXEXTRACT(B150,"(?&lt;=//)[^/]+")</f>
@@ -17268,7 +17277,7 @@
         <v>1829</v>
       </c>
       <c r="S150" s="1" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="T150" s="1">
         <v>0</v>
@@ -17298,7 +17307,7 @@
         <v>1496</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>49</v>
@@ -17361,7 +17370,7 @@
         <v>127</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>324</v>
@@ -17373,7 +17382,7 @@
         <v>4</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="L152" s="1" t="str" cm="1">
         <f t="array" ref="L152">_xlfn.REGEXEXTRACT(B152,"(?&lt;=//)[^/]+")</f>
@@ -17427,7 +17436,7 @@
         <v>63</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>321</v>
@@ -17493,7 +17502,7 @@
         <v>63</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>461</v>
@@ -17505,7 +17514,7 @@
         <v>4</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="L154" s="1" t="str" cm="1">
         <f t="array" ref="L154">_xlfn.REGEXEXTRACT(B154,"(?&lt;=//)[^/]+")</f>
@@ -17562,7 +17571,7 @@
         <v>389</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>49</v>
@@ -17628,7 +17637,7 @@
         <v>451</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>49</v>
@@ -17769,7 +17778,7 @@
         <v>4</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="L158" s="1" t="str" cm="1">
         <f t="array" ref="L158">_xlfn.REGEXEXTRACT(B158,"(?&lt;=//)[^/]+")</f>
@@ -17892,7 +17901,7 @@
         <v>380</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>49</v>
@@ -17958,7 +17967,7 @@
         <v>449</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>49</v>
@@ -18090,7 +18099,7 @@
         <v>596</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>49</v>
@@ -18099,7 +18108,7 @@
         <v>4</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="L163" s="1" t="str" cm="1">
         <f t="array" ref="L163">_xlfn.REGEXEXTRACT(B163,"(?&lt;=//)[^/]+")</f>
@@ -18156,7 +18165,7 @@
         <v>305</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>49</v>
@@ -18165,7 +18174,7 @@
         <v>4</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="L164" s="1" t="str" cm="1">
         <f t="array" ref="L164">_xlfn.REGEXEXTRACT(B164,"(?&lt;=//)[^/]+")</f>
@@ -18321,10 +18330,10 @@
         <v>1</v>
       </c>
       <c r="R166" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="S166" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="T166" s="1">
         <v>0</v>
@@ -18354,7 +18363,7 @@
         <v>413</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>49</v>
@@ -18453,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="S168" s="1" t="s">
         <v>1553</v>
@@ -18483,10 +18492,10 @@
         <v>53</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>49</v>
@@ -18618,7 +18627,7 @@
         <v>868</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>49</v>
@@ -18816,7 +18825,7 @@
         <v>889</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>49</v>
@@ -18879,10 +18888,10 @@
         <v>54</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>49</v>
@@ -18891,7 +18900,7 @@
         <v>4</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="L175" s="1" t="str" cm="1">
         <f t="array" ref="L175">_xlfn.REGEXEXTRACT(B175,"(?&lt;=//)[^/]+")</f>
@@ -18942,13 +18951,13 @@
         <v>198</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>357</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>49</v>
@@ -19011,10 +19020,10 @@
         <v>54</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>49</v>
@@ -19080,7 +19089,7 @@
         <v>304</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>49</v>
@@ -19113,7 +19122,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="S178" s="1" t="s">
         <v>1462</v>
@@ -19146,7 +19155,7 @@
         <v>1216</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>49</v>
@@ -19179,10 +19188,10 @@
         <v>1</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="S179" s="1" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="T179" s="1">
         <v>0</v>
@@ -19209,7 +19218,7 @@
         <v>63</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>474</v>
@@ -19221,7 +19230,7 @@
         <v>4</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="L180" s="1" t="str" cm="1">
         <f t="array" ref="L180">_xlfn.REGEXEXTRACT(B180,"(?&lt;=//)[^/]+")</f>
@@ -19275,10 +19284,10 @@
         <v>53</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>49</v>
@@ -19287,7 +19296,7 @@
         <v>4</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="L181" s="1" t="str" cm="1">
         <f t="array" ref="L181">_xlfn.REGEXEXTRACT(B181,"(?&lt;=//)[^/]+")</f>
@@ -19341,10 +19350,10 @@
         <v>53</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>49</v>
@@ -19353,7 +19362,7 @@
         <v>4</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="L182" s="1" t="str" cm="1">
         <f t="array" ref="L182">_xlfn.REGEXEXTRACT(B182,"(?&lt;=//)[^/]+")</f>
@@ -19377,10 +19386,10 @@
         <v>0</v>
       </c>
       <c r="R182" s="1" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="S182" s="1" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="T182" s="1">
         <v>7</v>
@@ -19407,7 +19416,7 @@
         <v>53</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>1224</v>
@@ -19473,7 +19482,7 @@
         <v>53</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>1224</v>
@@ -19509,10 +19518,10 @@
         <v>0</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="S184" s="1" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="T184" s="1">
         <v>8</v>
@@ -19539,10 +19548,10 @@
         <v>127</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>49</v>
@@ -19605,10 +19614,10 @@
         <v>127</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>49</v>
@@ -19668,13 +19677,13 @@
         <v>130</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>448</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>49</v>
@@ -19737,7 +19746,7 @@
         <v>128</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="H188" s="1" t="s">
         <v>1221</v>
@@ -19749,7 +19758,7 @@
         <v>3</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="L188" s="1" t="str" cm="1">
         <f t="array" ref="L188">_xlfn.REGEXEXTRACT(B188,"(?&lt;=//)[^/]+")</f>
@@ -19935,7 +19944,7 @@
         <v>63</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>461</v>
@@ -19947,7 +19956,7 @@
         <v>3</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="L191" s="1" t="str" cm="1">
         <f t="array" ref="L191">_xlfn.REGEXEXTRACT(B191,"(?&lt;=//)[^/]+")</f>
@@ -20067,7 +20076,7 @@
         <v>63</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>468</v>
@@ -20103,10 +20112,10 @@
         <v>0</v>
       </c>
       <c r="R193" s="1" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="S193" s="1" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="T193" s="1">
         <v>0</v>
@@ -20202,7 +20211,7 @@
         <v>393</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>49</v>
@@ -20268,7 +20277,7 @@
         <v>379</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>49</v>
@@ -20334,7 +20343,7 @@
         <v>443</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>49</v>
@@ -20466,7 +20475,7 @@
         <v>1560</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>49</v>
@@ -20598,7 +20607,7 @@
         <v>1228</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>49</v>
@@ -20646,7 +20655,7 @@
         <v>Done</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="C202" s="1">
         <v>44</v>
@@ -20730,7 +20739,7 @@
         <v>410</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>49</v>
@@ -20793,10 +20802,10 @@
         <v>53</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>49</v>
@@ -20805,7 +20814,7 @@
         <v>3</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="L204" s="1" t="str" cm="1">
         <f t="array" ref="L204">_xlfn.REGEXEXTRACT(B204,"(?&lt;=//)[^/]+")</f>
@@ -20898,7 +20907,7 @@
         <v>1586</v>
       </c>
       <c r="S205" s="1" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="T205" s="1">
         <v>0</v>
@@ -20910,7 +20919,7 @@
         <v>Done</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="C206" s="1">
         <v>102</v>
@@ -20925,10 +20934,10 @@
         <v>53</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>49</v>
@@ -21123,7 +21132,7 @@
         <v>63</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>462</v>
@@ -21201,7 +21210,7 @@
         <v>3</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="L210" s="1" t="str" cm="1">
         <f t="array" ref="L210">_xlfn.REGEXEXTRACT(B210,"(?&lt;=//)[^/]+")</f>
@@ -21240,7 +21249,7 @@
         <v>Done</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="C211" s="1">
         <v>37</v>
@@ -21258,7 +21267,7 @@
         <v>306</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>49</v>
@@ -21291,10 +21300,10 @@
         <v>0</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="S211" s="1" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="T211" s="1">
         <v>0</v>
@@ -21306,7 +21315,7 @@
         <v>Done</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C212" s="1">
         <v>19</v>
@@ -21321,10 +21330,10 @@
         <v>53</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>49</v>
@@ -21333,7 +21342,7 @@
         <v>3</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="L212" s="1" t="str" cm="1">
         <f t="array" ref="L212">_xlfn.REGEXEXTRACT(B212,"(?&lt;=//)[^/]+")</f>
@@ -21360,7 +21369,7 @@
         <v>1541</v>
       </c>
       <c r="S212" s="1" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="T212" s="1">
         <v>0</v>
@@ -21387,10 +21396,10 @@
         <v>53</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>49</v>
@@ -21399,7 +21408,7 @@
         <v>3</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="L213" s="1" t="str" cm="1">
         <f t="array" ref="L213">_xlfn.REGEXEXTRACT(B213,"(?&lt;=//)[^/]+")</f>
@@ -21453,10 +21462,10 @@
         <v>54</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>49</v>
@@ -21465,7 +21474,7 @@
         <v>3</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="L214" s="1" t="str" cm="1">
         <f t="array" ref="L214">_xlfn.REGEXEXTRACT(B214,"(?&lt;=//)[^/]+")</f>
@@ -21624,7 +21633,7 @@
         <v>1590</v>
       </c>
       <c r="S216" s="1" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="T216" s="1">
         <v>0</v>
@@ -21717,10 +21726,10 @@
         <v>54</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>49</v>
@@ -21756,7 +21765,7 @@
         <v>1630</v>
       </c>
       <c r="S218" s="1" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="T218" s="1">
         <v>0</v>
@@ -21786,7 +21795,7 @@
         <v>391</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>49</v>
@@ -21819,7 +21828,7 @@
         <v>0</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="S219" s="1" t="s">
         <v>1678</v>
@@ -21918,7 +21927,7 @@
         <v>870</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>49</v>
@@ -21978,13 +21987,13 @@
         <v>191</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>482</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>49</v>
@@ -22047,7 +22056,7 @@
         <v>53</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>835</v>
@@ -22059,7 +22068,7 @@
         <v>2</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="L223" s="1" t="str" cm="1">
         <f t="array" ref="L223">_xlfn.REGEXEXTRACT(B223,"(?&lt;=//)[^/]+")</f>
@@ -22110,13 +22119,13 @@
         <v>59</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>49</v>
@@ -22182,7 +22191,7 @@
         <v>1589</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>49</v>
@@ -22218,7 +22227,7 @@
         <v>1587</v>
       </c>
       <c r="S225" s="1" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="T225" s="1">
         <v>0</v>
@@ -22311,10 +22320,10 @@
         <v>53</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>49</v>
@@ -22323,7 +22332,7 @@
         <v>1</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="L227" s="1" t="str" cm="1">
         <f t="array" ref="L227">_xlfn.REGEXEXTRACT(B227,"(?&lt;=//)[^/]+")</f>
@@ -22377,7 +22386,7 @@
         <v>54</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>55</v>
@@ -22389,7 +22398,7 @@
         <v>1</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="L228" s="1" t="str" cm="1">
         <f t="array" ref="L228">_xlfn.REGEXEXTRACT(B228,"(?&lt;=//)[^/]+")</f>
@@ -22529,10 +22538,10 @@
         <v>0</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="S230" s="1" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="T230" s="1">
         <v>0</v>
@@ -22643,10 +22652,10 @@
         <v>0</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="S232" s="1" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="T232" s="1">
         <v>0</v>
@@ -22673,10 +22682,10 @@
         <v>53</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>49</v>
@@ -22685,7 +22694,7 @@
         <v>5</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="L233" s="1" t="str" cm="1">
         <f t="array" ref="L233">_xlfn.REGEXEXTRACT(B233,"(?&lt;=//)[^/]+")</f>
@@ -22709,10 +22718,10 @@
         <v>1</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="S233" s="1" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="T233" s="1">
         <v>1</v>
@@ -22825,10 +22834,10 @@
         <v>1</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="S235" s="1" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="T235" s="1">
         <v>1</v>
@@ -22858,7 +22867,7 @@
         <v>792</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
@@ -23026,13 +23035,13 @@
         <v>115</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>351</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="I239" s="1"/>
       <c r="J239" s="1"/>
@@ -23150,7 +23159,7 @@
         <v>792</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="I241" s="1"/>
       <c r="J241" s="1"/>
@@ -23321,7 +23330,7 @@
         <v>53</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -23469,10 +23478,10 @@
         <v>1</v>
       </c>
       <c r="R246" s="1" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="S246" s="1" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="T246" s="1">
         <v>0</v>
@@ -23873,10 +23882,10 @@
         <v>1</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="S253" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="T253" s="1">
         <v>0</v>
@@ -23904,7 +23913,7 @@
       </c>
       <c r="G254" s="1"/>
       <c r="H254" s="1" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -23989,10 +23998,10 @@
         <v>1</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="S255" s="1" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="T255" s="1">
         <v>3</v>
@@ -24047,10 +24056,10 @@
         <v>1</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="S256" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="T256" s="1">
         <v>1</v>
@@ -24133,10 +24142,10 @@
         <v>53</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -24252,7 +24261,7 @@
         <v>1849</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -24309,7 +24318,7 @@
         <v>53</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
@@ -24395,10 +24404,10 @@
         <v>0</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="S262" s="1" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="T262" s="1">
         <v>0</v>
@@ -24591,7 +24600,7 @@
         <v>627</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>54</v>
@@ -24739,10 +24748,10 @@
         <v>0</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="S268" s="1" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="T268" s="1">
         <v>0</v>
@@ -24886,7 +24895,7 @@
         <v>1035</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="I271" s="1"/>
       <c r="J271" s="1"/>
@@ -25115,7 +25124,7 @@
         <v>53</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="H275" s="1"/>
       <c r="I275" s="1"/>
@@ -25431,10 +25440,10 @@
         <v>1</v>
       </c>
       <c r="R280" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="S280" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="T280" s="1">
         <v>0</v>
@@ -25489,10 +25498,10 @@
         <v>1</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="S281" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="T281" s="1">
         <v>0</v>
@@ -25620,7 +25629,7 @@
         <v>Pending</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="C284" s="1">
         <v>47</v>
@@ -25663,10 +25672,10 @@
         <v>0</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="S284" s="1" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="T284" s="1">
         <v>4</v>
@@ -25694,7 +25703,7 @@
       </c>
       <c r="G285" s="1"/>
       <c r="H285" s="1" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -25814,7 +25823,7 @@
         <v>425</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -25904,7 +25913,7 @@
         <v>1536</v>
       </c>
       <c r="S288" s="1" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="T288" s="1">
         <v>0</v>
@@ -26015,10 +26024,10 @@
         <v>0</v>
       </c>
       <c r="R290" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="S290" s="1" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="T290" s="1">
         <v>0</v>
@@ -26045,7 +26054,7 @@
         <v>53</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="H291" s="1"/>
       <c r="I291" s="1"/>
@@ -26164,7 +26173,7 @@
         <v>855</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="I293" s="1"/>
       <c r="J293" s="1"/>
@@ -26387,7 +26396,7 @@
         <v>621</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>54</v>
@@ -26720,7 +26729,7 @@
     </row>
     <row r="303" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="str">
-        <f t="shared" ref="A303:A334" si="10">IF(ISBLANK(I303)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I303)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B303" s="1" t="s">
@@ -26733,7 +26742,7 @@
         <v>918</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>54</v>
@@ -26742,7 +26751,7 @@
         <v>866</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -26765,7 +26774,7 @@
         <v>1829</v>
       </c>
       <c r="Q303" s="1" t="b">
-        <f t="shared" ref="Q303:Q334" si="11">ISNUMBER(SEARCH(",",E303))</f>
+        <f>ISNUMBER(SEARCH(",",E303))</f>
         <v>1</v>
       </c>
       <c r="R303" s="1" t="s">
@@ -26780,7 +26789,7 @@
     </row>
     <row r="304" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I304)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B304" s="1" t="s">
@@ -26825,7 +26834,7 @@
         <v>1829</v>
       </c>
       <c r="Q304" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E304))</f>
         <v>0</v>
       </c>
       <c r="R304" s="1" t="s">
@@ -26840,7 +26849,7 @@
     </row>
     <row r="305" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I305)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B305" s="1" t="s">
@@ -26860,7 +26869,7 @@
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="1" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -26883,7 +26892,7 @@
         <v>1829</v>
       </c>
       <c r="Q305" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E305))</f>
         <v>0</v>
       </c>
       <c r="R305" s="1" t="s">
@@ -26898,7 +26907,7 @@
     </row>
     <row r="306" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I306)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B306" s="1" t="s">
@@ -26939,7 +26948,7 @@
         <v>1829</v>
       </c>
       <c r="Q306" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E306))</f>
         <v>0</v>
       </c>
       <c r="R306" s="1" t="s">
@@ -26954,7 +26963,7 @@
     </row>
     <row r="307" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I307)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B307" s="1" t="s">
@@ -26995,7 +27004,7 @@
         <v>1829</v>
       </c>
       <c r="Q307" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E307))</f>
         <v>0</v>
       </c>
       <c r="R307" s="1" t="s">
@@ -27010,7 +27019,7 @@
     </row>
     <row r="308" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I308)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B308" s="1" t="s">
@@ -27051,7 +27060,7 @@
         <v>1829</v>
       </c>
       <c r="Q308" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E308))</f>
         <v>0</v>
       </c>
       <c r="R308" s="1" t="s">
@@ -27066,7 +27075,7 @@
     </row>
     <row r="309" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I309)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B309" s="1" t="s">
@@ -27109,7 +27118,7 @@
         <v>1829</v>
       </c>
       <c r="Q309" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E309))</f>
         <v>1</v>
       </c>
       <c r="R309" s="1" t="s">
@@ -27124,7 +27133,7 @@
     </row>
     <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I310)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B310" s="1" t="s">
@@ -27165,7 +27174,7 @@
         <v>1829</v>
       </c>
       <c r="Q310" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E310))</f>
         <v>0</v>
       </c>
       <c r="R310" s="1" t="s">
@@ -27180,7 +27189,7 @@
     </row>
     <row r="311" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I311)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B311" s="1" t="s">
@@ -27193,7 +27202,7 @@
         <v>622</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>54</v>
@@ -27225,7 +27234,7 @@
         <v>1829</v>
       </c>
       <c r="Q311" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E311))</f>
         <v>1</v>
       </c>
       <c r="R311" s="1" t="s">
@@ -27240,7 +27249,7 @@
     </row>
     <row r="312" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I312)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B312" s="1" t="s">
@@ -27283,7 +27292,7 @@
         <v>1829</v>
       </c>
       <c r="Q312" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E312))</f>
         <v>0</v>
       </c>
       <c r="R312" s="1" t="s">
@@ -27298,7 +27307,7 @@
     </row>
     <row r="313" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I313)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B313" s="1" t="s">
@@ -27318,7 +27327,7 @@
       </c>
       <c r="G313" s="1"/>
       <c r="H313" s="1" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -27341,7 +27350,7 @@
         <v>1829</v>
       </c>
       <c r="Q313" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E313))</f>
         <v>0</v>
       </c>
       <c r="R313" s="1" t="s">
@@ -27356,7 +27365,7 @@
     </row>
     <row r="314" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I314)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B314" s="1" t="s">
@@ -27401,14 +27410,14 @@
         <v>1829</v>
       </c>
       <c r="Q314" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E314))</f>
         <v>1</v>
       </c>
       <c r="R314" s="1" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="S314" s="1" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="T314" s="1">
         <v>0</v>
@@ -27416,7 +27425,7 @@
     </row>
     <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I315)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B315" s="1" t="s">
@@ -27461,7 +27470,7 @@
         <v>1829</v>
       </c>
       <c r="Q315" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E315))</f>
         <v>0</v>
       </c>
       <c r="R315" s="1" t="s">
@@ -27476,7 +27485,7 @@
     </row>
     <row r="316" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I316)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B316" s="1" t="s">
@@ -27495,7 +27504,7 @@
         <v>54</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="H316" s="1"/>
       <c r="I316" s="1"/>
@@ -27519,7 +27528,7 @@
         <v>1829</v>
       </c>
       <c r="Q316" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E316))</f>
         <v>1</v>
       </c>
       <c r="R316" s="1" t="s">
@@ -27534,7 +27543,7 @@
     </row>
     <row r="317" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I317)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B317" s="1" t="s">
@@ -27547,7 +27556,7 @@
         <v>918</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>54</v>
@@ -27577,7 +27586,7 @@
         <v>1829</v>
       </c>
       <c r="Q317" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E317))</f>
         <v>1</v>
       </c>
       <c r="R317" s="1" t="s">
@@ -27592,7 +27601,7 @@
     </row>
     <row r="318" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I318)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B318" s="1" t="s">
@@ -27635,7 +27644,7 @@
         <v>1829</v>
       </c>
       <c r="Q318" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E318))</f>
         <v>0</v>
       </c>
       <c r="R318" s="1" t="s">
@@ -27650,7 +27659,7 @@
     </row>
     <row r="319" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I319)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B319" s="1" t="s">
@@ -27663,7 +27672,7 @@
         <v>622</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>54</v>
@@ -27693,7 +27702,7 @@
         <v>1829</v>
       </c>
       <c r="Q319" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E319))</f>
         <v>1</v>
       </c>
       <c r="R319" s="1" t="s">
@@ -27706,9 +27715,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I320)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B320" s="1" t="s">
@@ -27727,10 +27736,10 @@
         <v>53</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>49</v>
@@ -27739,7 +27748,7 @@
         <v>8</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="L320" s="1" t="str" cm="1">
         <f t="array" ref="L320">_xlfn.REGEXEXTRACT(B320,"(?&lt;=//)[^/]+")</f>
@@ -27759,7 +27768,7 @@
         <v>1829</v>
       </c>
       <c r="Q320" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E320))</f>
         <v>0</v>
       </c>
       <c r="R320" s="1" t="s">
@@ -27772,9 +27781,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I321)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B321" s="1" t="s">
@@ -27793,10 +27802,10 @@
         <v>54</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>49</v>
@@ -27805,7 +27814,7 @@
         <v>7</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="L321" s="1" t="str" cm="1">
         <f t="array" ref="L321">_xlfn.REGEXEXTRACT(B321,"(?&lt;=//)[^/]+")</f>
@@ -27825,7 +27834,7 @@
         <v>1829</v>
       </c>
       <c r="Q321" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E321))</f>
         <v>1</v>
       </c>
       <c r="R321" s="1" t="s">
@@ -27840,7 +27849,7 @@
     </row>
     <row r="322" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I322)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B322" s="1" t="s">
@@ -27883,7 +27892,7 @@
         <v>1829</v>
       </c>
       <c r="Q322" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E322))</f>
         <v>0</v>
       </c>
       <c r="R322" s="1" t="s">
@@ -27898,7 +27907,7 @@
     </row>
     <row r="323" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I323)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B323" s="1" t="s">
@@ -27941,7 +27950,7 @@
         <v>1829</v>
       </c>
       <c r="Q323" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E323))</f>
         <v>0</v>
       </c>
       <c r="R323" s="1" t="s">
@@ -27956,7 +27965,7 @@
     </row>
     <row r="324" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I324)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B324" s="1" t="s">
@@ -27999,7 +28008,7 @@
         <v>1829</v>
       </c>
       <c r="Q324" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E324))</f>
         <v>0</v>
       </c>
       <c r="R324" s="1" t="s">
@@ -28014,7 +28023,7 @@
     </row>
     <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I325)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B325" s="1" t="s">
@@ -28057,7 +28066,7 @@
         <v>1829</v>
       </c>
       <c r="Q325" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E325))</f>
         <v>1</v>
       </c>
       <c r="R325" s="1" t="s">
@@ -28072,7 +28081,7 @@
     </row>
     <row r="326" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I326)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B326" s="1" t="s">
@@ -28115,14 +28124,14 @@
         <v>1829</v>
       </c>
       <c r="Q326" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E326))</f>
         <v>1</v>
       </c>
       <c r="R326" s="1" t="s">
         <v>1593</v>
       </c>
       <c r="S326" s="1" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="T326" s="1">
         <v>3</v>
@@ -28130,7 +28139,7 @@
     </row>
     <row r="327" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I327)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B327" s="1" t="s">
@@ -28143,7 +28152,7 @@
         <v>625</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>54</v>
@@ -28173,7 +28182,7 @@
         <v>1829</v>
       </c>
       <c r="Q327" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E327))</f>
         <v>1</v>
       </c>
       <c r="R327" s="1" t="s">
@@ -28188,7 +28197,7 @@
     </row>
     <row r="328" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I328)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B328" s="1" t="s">
@@ -28208,7 +28217,7 @@
       </c>
       <c r="G328" s="1"/>
       <c r="H328" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="I328" s="1"/>
       <c r="J328" s="1"/>
@@ -28231,7 +28240,7 @@
         <v>1829</v>
       </c>
       <c r="Q328" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E328))</f>
         <v>0</v>
       </c>
       <c r="R328" s="1" t="s">
@@ -28246,7 +28255,7 @@
     </row>
     <row r="329" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I329)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B329" s="1" t="s">
@@ -28269,7 +28278,7 @@
       <c r="I329" s="1"/>
       <c r="J329" s="1"/>
       <c r="K329" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="L329" s="1" t="str" cm="1">
         <f t="array" ref="L329">_xlfn.REGEXEXTRACT(B329,"(?&lt;=//)[^/]+")</f>
@@ -28289,7 +28298,7 @@
         <v>1829</v>
       </c>
       <c r="Q329" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E329))</f>
         <v>0</v>
       </c>
       <c r="R329" s="1" t="s">
@@ -28304,7 +28313,7 @@
     </row>
     <row r="330" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I330)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B330" s="1" t="s">
@@ -28345,7 +28354,7 @@
         <v>1829</v>
       </c>
       <c r="Q330" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E330))</f>
         <v>0</v>
       </c>
       <c r="R330" s="1" t="s">
@@ -28360,7 +28369,7 @@
     </row>
     <row r="331" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I331)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B331" s="1" t="s">
@@ -28401,14 +28410,14 @@
         <v>1829</v>
       </c>
       <c r="Q331" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E331))</f>
         <v>0</v>
       </c>
       <c r="R331" s="1" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="S331" s="1" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="T331" s="1">
         <v>0</v>
@@ -28416,7 +28425,7 @@
     </row>
     <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I332)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B332" s="1" t="s">
@@ -28457,7 +28466,7 @@
         <v>1829</v>
       </c>
       <c r="Q332" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E332))</f>
         <v>0</v>
       </c>
       <c r="R332" s="1" t="s">
@@ -28472,7 +28481,7 @@
     </row>
     <row r="333" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I333)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B333" s="1" t="s">
@@ -28515,7 +28524,7 @@
         <v>1829</v>
       </c>
       <c r="Q333" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E333))</f>
         <v>0</v>
       </c>
       <c r="R333" s="1" t="s">
@@ -28528,9 +28537,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(I334)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B334" s="1" t="s">
@@ -28549,10 +28558,10 @@
         <v>53</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>49</v>
@@ -28561,7 +28570,7 @@
         <v>6</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="L334" s="1" t="str" cm="1">
         <f t="array" ref="L334">_xlfn.REGEXEXTRACT(B334,"(?&lt;=//)[^/]+")</f>
@@ -28581,14 +28590,14 @@
         <v>1829</v>
       </c>
       <c r="Q334" s="1" t="b">
-        <f t="shared" si="11"/>
+        <f>ISNUMBER(SEARCH(",",E334))</f>
         <v>0</v>
       </c>
       <c r="R334" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="S334" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="T334" s="1">
         <v>8</v>
@@ -28596,7 +28605,7 @@
     </row>
     <row r="335" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="str">
-        <f t="shared" ref="A335:A366" si="12">IF(ISBLANK(I335)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I335)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B335" s="1" t="s">
@@ -28641,7 +28650,7 @@
         <v>1829</v>
       </c>
       <c r="Q335" s="1" t="b">
-        <f t="shared" ref="Q335:Q366" si="13">ISNUMBER(SEARCH(",",E335))</f>
+        <f>ISNUMBER(SEARCH(",",E335))</f>
         <v>1</v>
       </c>
       <c r="R335" s="1" t="s">
@@ -28656,7 +28665,7 @@
     </row>
     <row r="336" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I336)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B336" s="1" t="s">
@@ -28699,7 +28708,7 @@
         <v>1829</v>
       </c>
       <c r="Q336" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E336))</f>
         <v>1</v>
       </c>
       <c r="R336" s="1" t="s">
@@ -28714,7 +28723,7 @@
     </row>
     <row r="337" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I337)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B337" s="1" t="s">
@@ -28757,7 +28766,7 @@
         <v>1829</v>
       </c>
       <c r="Q337" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E337))</f>
         <v>0</v>
       </c>
       <c r="R337" s="1" t="s">
@@ -28772,7 +28781,7 @@
     </row>
     <row r="338" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I338)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B338" s="1" t="s">
@@ -28815,14 +28824,14 @@
         <v>1829</v>
       </c>
       <c r="Q338" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E338))</f>
         <v>0</v>
       </c>
       <c r="R338" s="1" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="S338" s="1" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="T338" s="1">
         <v>0</v>
@@ -28830,7 +28839,7 @@
     </row>
     <row r="339" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I339)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B339" s="1" t="s">
@@ -28873,7 +28882,7 @@
         <v>1829</v>
       </c>
       <c r="Q339" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E339))</f>
         <v>0</v>
       </c>
       <c r="R339" s="1" t="s">
@@ -28888,7 +28897,7 @@
     </row>
     <row r="340" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I340)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B340" s="1" t="s">
@@ -28935,7 +28944,7 @@
         <v>1829</v>
       </c>
       <c r="Q340" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E340))</f>
         <v>0</v>
       </c>
       <c r="R340" s="1" t="s">
@@ -28950,7 +28959,7 @@
     </row>
     <row r="341" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I341)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B341" s="1" t="s">
@@ -28991,14 +29000,14 @@
         <v>1829</v>
       </c>
       <c r="Q341" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E341))</f>
         <v>0</v>
       </c>
       <c r="R341" s="1" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="S341" s="1" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="T341" s="1">
         <v>0</v>
@@ -29006,7 +29015,7 @@
     </row>
     <row r="342" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I342)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B342" s="1" t="s">
@@ -29047,7 +29056,7 @@
         <v>1829</v>
       </c>
       <c r="Q342" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E342))</f>
         <v>0</v>
       </c>
       <c r="R342" s="1" t="s">
@@ -29062,7 +29071,7 @@
     </row>
     <row r="343" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I343)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B343" s="1" t="s">
@@ -29105,22 +29114,22 @@
         <v>1829</v>
       </c>
       <c r="Q343" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E343))</f>
         <v>1</v>
       </c>
       <c r="R343" s="1" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="S343" s="1" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="T343" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I344)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B344" s="1" t="s">
@@ -29139,10 +29148,10 @@
         <v>54</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>49</v>
@@ -29151,7 +29160,7 @@
         <v>8</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="L344" s="1" t="str" cm="1">
         <f t="array" ref="L344">_xlfn.REGEXEXTRACT(B344,"(?&lt;=//)[^/]+")</f>
@@ -29171,7 +29180,7 @@
         <v>1829</v>
       </c>
       <c r="Q344" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E344))</f>
         <v>1</v>
       </c>
       <c r="R344" s="1" t="s">
@@ -29186,7 +29195,7 @@
     </row>
     <row r="345" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I345)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B345" s="1" t="s">
@@ -29205,7 +29214,7 @@
         <v>53</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H345" s="1"/>
       <c r="I345" s="1"/>
@@ -29229,7 +29238,7 @@
         <v>1829</v>
       </c>
       <c r="Q345" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E345))</f>
         <v>0</v>
       </c>
       <c r="R345" s="1" t="s">
@@ -29242,9 +29251,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I346)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B346" s="1" t="s">
@@ -29263,10 +29272,10 @@
         <v>53</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>49</v>
@@ -29275,7 +29284,7 @@
         <v>8</v>
       </c>
       <c r="K346" s="1" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="L346" s="1" t="str" cm="1">
         <f t="array" ref="L346">_xlfn.REGEXEXTRACT(B346,"(?&lt;=//)[^/]+")</f>
@@ -29295,7 +29304,7 @@
         <v>1829</v>
       </c>
       <c r="Q346" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E346))</f>
         <v>0</v>
       </c>
       <c r="R346" s="1" t="s">
@@ -29310,7 +29319,7 @@
     </row>
     <row r="347" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I347)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B347" s="1" t="s">
@@ -29351,14 +29360,14 @@
         <v>1829</v>
       </c>
       <c r="Q347" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E347))</f>
         <v>0</v>
       </c>
       <c r="R347" s="1" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="S347" s="1" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="T347" s="1">
         <v>0</v>
@@ -29366,7 +29375,7 @@
     </row>
     <row r="348" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I348)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B348" s="1" t="s">
@@ -29407,14 +29416,14 @@
         <v>1829</v>
       </c>
       <c r="Q348" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E348))</f>
         <v>0</v>
       </c>
       <c r="R348" s="1" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="S348" s="1" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="T348" s="1">
         <v>0</v>
@@ -29422,7 +29431,7 @@
     </row>
     <row r="349" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I349)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B349" s="1" t="s">
@@ -29435,7 +29444,7 @@
         <v>618</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>53</v>
@@ -29465,7 +29474,7 @@
         <v>1829</v>
       </c>
       <c r="Q349" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E349))</f>
         <v>1</v>
       </c>
       <c r="R349" s="1" t="s">
@@ -29480,7 +29489,7 @@
     </row>
     <row r="350" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I350)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B350" s="1" t="s">
@@ -29521,7 +29530,7 @@
         <v>1829</v>
       </c>
       <c r="Q350" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E350))</f>
         <v>0</v>
       </c>
       <c r="R350" s="1" t="s">
@@ -29534,10 +29543,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>Pending</v>
+        <f>IF(ISBLANK(I351)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>1201</v>
@@ -29555,14 +29564,20 @@
         <v>53</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1856</v>
+        <v>2306</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>2052</v>
-      </c>
-      <c r="I351" s="1"/>
-      <c r="J351" s="1"/>
-      <c r="K351" s="1"/>
+        <v>2305</v>
+      </c>
+      <c r="I351" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J351" s="1">
+        <v>7</v>
+      </c>
+      <c r="K351" s="1" t="s">
+        <v>2304</v>
+      </c>
       <c r="L351" s="1" t="str" cm="1">
         <f t="array" ref="L351">_xlfn.REGEXEXTRACT(B351,"(?&lt;=//)[^/]+")</f>
         <v>hcbdsm.com</v>
@@ -29581,7 +29596,7 @@
         <v>1829</v>
       </c>
       <c r="Q351" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E351))</f>
         <v>0</v>
       </c>
       <c r="R351" s="1" t="s">
@@ -29596,7 +29611,7 @@
     </row>
     <row r="352" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I352)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B352" s="1" t="s">
@@ -29615,10 +29630,10 @@
         <v>53</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
@@ -29641,7 +29656,7 @@
         <v>1829</v>
       </c>
       <c r="Q352" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E352))</f>
         <v>0</v>
       </c>
       <c r="R352" s="1" t="s">
@@ -29656,7 +29671,7 @@
     </row>
     <row r="353" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I353)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B353" s="1" t="s">
@@ -29699,7 +29714,7 @@
         <v>1829</v>
       </c>
       <c r="Q353" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E353))</f>
         <v>1</v>
       </c>
       <c r="R353" s="1" t="s">
@@ -29714,7 +29729,7 @@
     </row>
     <row r="354" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I354)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B354" s="1" t="s">
@@ -29755,7 +29770,7 @@
         <v>1829</v>
       </c>
       <c r="Q354" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E354))</f>
         <v>0</v>
       </c>
       <c r="R354" s="1" t="s">
@@ -29770,7 +29785,7 @@
     </row>
     <row r="355" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I355)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B355" s="1" t="s">
@@ -29813,7 +29828,7 @@
         <v>1829</v>
       </c>
       <c r="Q355" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E355))</f>
         <v>0</v>
       </c>
       <c r="R355" s="1" t="s">
@@ -29828,7 +29843,7 @@
     </row>
     <row r="356" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I356)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B356" s="1" t="s">
@@ -29847,10 +29862,10 @@
         <v>53</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I356" s="1"/>
       <c r="J356" s="1"/>
@@ -29873,7 +29888,7 @@
         <v>1829</v>
       </c>
       <c r="Q356" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E356))</f>
         <v>0</v>
       </c>
       <c r="R356" s="1" t="s">
@@ -29888,7 +29903,7 @@
     </row>
     <row r="357" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I357)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B357" s="1" t="s">
@@ -29931,7 +29946,7 @@
         <v>1829</v>
       </c>
       <c r="Q357" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E357))</f>
         <v>0</v>
       </c>
       <c r="R357" s="1" t="s">
@@ -29946,7 +29961,7 @@
     </row>
     <row r="358" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I358)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B358" s="1" t="s">
@@ -29987,7 +30002,7 @@
         <v>1829</v>
       </c>
       <c r="Q358" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E358))</f>
         <v>0</v>
       </c>
       <c r="R358" s="1" t="s">
@@ -30002,8 +30017,8 @@
     </row>
     <row r="359" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>Pending</v>
+        <f>IF(ISBLANK(I359)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>817</v>
@@ -30021,14 +30036,20 @@
         <v>53</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>1865</v>
+        <v>2308</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>2069</v>
-      </c>
-      <c r="I359" s="1"/>
-      <c r="J359" s="1"/>
-      <c r="K359" s="1"/>
+        <v>2067</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J359" s="1">
+        <v>8</v>
+      </c>
+      <c r="K359" s="1" t="s">
+        <v>2307</v>
+      </c>
       <c r="L359" s="1" t="str" cm="1">
         <f t="array" ref="L359">_xlfn.REGEXEXTRACT(B359,"(?&lt;=//)[^/]+")</f>
         <v>hcbdsm.com</v>
@@ -30047,7 +30068,7 @@
         <v>1829</v>
       </c>
       <c r="Q359" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E359))</f>
         <v>0</v>
       </c>
       <c r="R359" s="1" t="s">
@@ -30062,7 +30083,7 @@
     </row>
     <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I360)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B360" s="1" t="s">
@@ -30105,7 +30126,7 @@
         <v>1829</v>
       </c>
       <c r="Q360" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E360))</f>
         <v>1</v>
       </c>
       <c r="R360" s="1" t="s">
@@ -30120,7 +30141,7 @@
     </row>
     <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I361)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B361" s="1" t="s">
@@ -30165,7 +30186,7 @@
         <v>1829</v>
       </c>
       <c r="Q361" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E361))</f>
         <v>1</v>
       </c>
       <c r="R361" s="1" t="s">
@@ -30180,7 +30201,7 @@
     </row>
     <row r="362" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I362)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B362" s="1" t="s">
@@ -30223,7 +30244,7 @@
         <v>1829</v>
       </c>
       <c r="Q362" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E362))</f>
         <v>1</v>
       </c>
       <c r="R362" s="1" t="s">
@@ -30238,7 +30259,7 @@
     </row>
     <row r="363" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I363)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B363" s="1" t="s">
@@ -30281,7 +30302,7 @@
         <v>1829</v>
       </c>
       <c r="Q363" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E363))</f>
         <v>0</v>
       </c>
       <c r="R363" s="1" t="s">
@@ -30296,7 +30317,7 @@
     </row>
     <row r="364" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I364)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B364" s="1" t="s">
@@ -30315,7 +30336,7 @@
         <v>53</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="H364" s="1"/>
       <c r="I364" s="1"/>
@@ -30339,7 +30360,7 @@
         <v>1829</v>
       </c>
       <c r="Q364" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E364))</f>
         <v>1</v>
       </c>
       <c r="R364" s="1" t="s">
@@ -30354,7 +30375,7 @@
     </row>
     <row r="365" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I365)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B365" s="1" t="s">
@@ -30367,7 +30388,7 @@
         <v>623</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="F365" s="1" t="s">
         <v>54</v>
@@ -30397,7 +30418,7 @@
         <v>1829</v>
       </c>
       <c r="Q365" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E365))</f>
         <v>1</v>
       </c>
       <c r="R365" s="1" t="s">
@@ -30412,7 +30433,7 @@
     </row>
     <row r="366" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(ISBLANK(I366)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B366" s="1" t="s">
@@ -30455,7 +30476,7 @@
         <v>1829</v>
       </c>
       <c r="Q366" s="1" t="b">
-        <f t="shared" si="13"/>
+        <f>ISNUMBER(SEARCH(",",E366))</f>
         <v>1</v>
       </c>
       <c r="R366" s="1" t="s">
@@ -30470,7 +30491,7 @@
     </row>
     <row r="367" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="str">
-        <f t="shared" ref="A367:A398" si="14">IF(ISBLANK(I367)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I367)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B367" s="1" t="s">
@@ -30515,7 +30536,7 @@
         <v>1829</v>
       </c>
       <c r="Q367" s="1" t="b">
-        <f t="shared" ref="Q367:Q398" si="15">ISNUMBER(SEARCH(",",E367))</f>
+        <f>ISNUMBER(SEARCH(",",E367))</f>
         <v>1</v>
       </c>
       <c r="R367" s="1" t="s">
@@ -30530,7 +30551,7 @@
     </row>
     <row r="368" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I368)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B368" s="1" t="s">
@@ -30552,7 +30573,7 @@
         <v>1854</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -30575,7 +30596,7 @@
         <v>1829</v>
       </c>
       <c r="Q368" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E368))</f>
         <v>0</v>
       </c>
       <c r="R368" s="1" t="s">
@@ -30590,7 +30611,7 @@
     </row>
     <row r="369" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I369)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B369" s="1" t="s">
@@ -30603,13 +30624,13 @@
         <v>623</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="H369" s="1"/>
       <c r="I369" s="1"/>
@@ -30633,7 +30654,7 @@
         <v>1829</v>
       </c>
       <c r="Q369" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E369))</f>
         <v>1</v>
       </c>
       <c r="R369" s="1" t="s">
@@ -30648,7 +30669,7 @@
     </row>
     <row r="370" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I370)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B370" s="1" t="s">
@@ -30668,7 +30689,7 @@
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="1" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -30691,14 +30712,14 @@
         <v>1829</v>
       </c>
       <c r="Q370" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E370))</f>
         <v>0</v>
       </c>
       <c r="R370" s="1" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="S370" s="1" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="T370" s="1">
         <v>4</v>
@@ -30706,7 +30727,7 @@
     </row>
     <row r="371" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I371)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B371" s="1" t="s">
@@ -30747,14 +30768,14 @@
         <v>1829</v>
       </c>
       <c r="Q371" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E371))</f>
         <v>0</v>
       </c>
       <c r="R371" s="1" t="s">
         <v>1731</v>
       </c>
       <c r="S371" s="1" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="T371" s="1">
         <v>0</v>
@@ -30762,7 +30783,7 @@
     </row>
     <row r="372" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I372)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B372" s="1" t="s">
@@ -30805,7 +30826,7 @@
         <v>1829</v>
       </c>
       <c r="Q372" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E372))</f>
         <v>0</v>
       </c>
       <c r="R372" s="1" t="s">
@@ -30820,7 +30841,7 @@
     </row>
     <row r="373" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I373)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B373" s="1" t="s">
@@ -30863,14 +30884,14 @@
         <v>1829</v>
       </c>
       <c r="Q373" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E373))</f>
         <v>0</v>
       </c>
       <c r="R373" s="1" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="S373" s="1" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="T373" s="1">
         <v>0</v>
@@ -30878,7 +30899,7 @@
     </row>
     <row r="374" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I374)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B374" s="1" t="s">
@@ -30919,14 +30940,14 @@
         <v>1829</v>
       </c>
       <c r="Q374" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E374))</f>
         <v>0</v>
       </c>
       <c r="R374" s="1" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="S374" s="1" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="T374" s="1">
         <v>0</v>
@@ -30934,7 +30955,7 @@
     </row>
     <row r="375" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I375)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B375" s="1" t="s">
@@ -30977,14 +30998,14 @@
         <v>1829</v>
       </c>
       <c r="Q375" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E375))</f>
         <v>1</v>
       </c>
       <c r="R375" s="1" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="S375" s="1" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="T375" s="1">
         <v>0</v>
@@ -30992,7 +31013,7 @@
     </row>
     <row r="376" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I376)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B376" s="1" t="s">
@@ -31035,7 +31056,7 @@
         <v>1829</v>
       </c>
       <c r="Q376" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E376))</f>
         <v>1</v>
       </c>
       <c r="R376" s="1" t="s">
@@ -31050,7 +31071,7 @@
     </row>
     <row r="377" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I377)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B377" s="1" t="s">
@@ -31069,10 +31090,10 @@
         <v>53</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -31095,7 +31116,7 @@
         <v>1829</v>
       </c>
       <c r="Q377" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E377))</f>
         <v>0</v>
       </c>
       <c r="R377" s="1" t="s">
@@ -31110,7 +31131,7 @@
     </row>
     <row r="378" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I378)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B378" s="1" t="s">
@@ -31153,7 +31174,7 @@
         <v>1829</v>
       </c>
       <c r="Q378" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E378))</f>
         <v>0</v>
       </c>
       <c r="R378" s="1" t="s">
@@ -31168,7 +31189,7 @@
     </row>
     <row r="379" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I379)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B379" s="1" t="s">
@@ -31187,7 +31208,7 @@
         <v>53</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -31211,7 +31232,7 @@
         <v>1829</v>
       </c>
       <c r="Q379" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E379))</f>
         <v>0</v>
       </c>
       <c r="R379" s="1" t="s">
@@ -31226,7 +31247,7 @@
     </row>
     <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I380)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B380" s="1" t="s">
@@ -31269,7 +31290,7 @@
         <v>1829</v>
       </c>
       <c r="Q380" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E380))</f>
         <v>0</v>
       </c>
       <c r="R380" s="1" t="s">
@@ -31284,7 +31305,7 @@
     </row>
     <row r="381" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I381)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B381" s="1" t="s">
@@ -31303,7 +31324,7 @@
         <v>53</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -31327,14 +31348,14 @@
         <v>1829</v>
       </c>
       <c r="Q381" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E381))</f>
         <v>0</v>
       </c>
       <c r="R381" s="1" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="S381" s="1" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="T381" s="1">
         <v>2</v>
@@ -31342,7 +31363,7 @@
     </row>
     <row r="382" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I382)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B382" s="1" t="s">
@@ -31385,7 +31406,7 @@
         <v>1829</v>
       </c>
       <c r="Q382" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E382))</f>
         <v>1</v>
       </c>
       <c r="R382" s="1" t="s">
@@ -31400,7 +31421,7 @@
     </row>
     <row r="383" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I383)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B383" s="1" t="s">
@@ -31441,7 +31462,7 @@
         <v>1829</v>
       </c>
       <c r="Q383" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E383))</f>
         <v>0</v>
       </c>
       <c r="R383" s="1" t="s">
@@ -31456,7 +31477,7 @@
     </row>
     <row r="384" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I384)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B384" s="1" t="s">
@@ -31497,14 +31518,14 @@
         <v>1829</v>
       </c>
       <c r="Q384" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E384))</f>
         <v>0</v>
       </c>
       <c r="R384" s="1" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="S384" s="1" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="T384" s="1">
         <v>0</v>
@@ -31512,7 +31533,7 @@
     </row>
     <row r="385" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I385)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B385" s="1" t="s">
@@ -31557,7 +31578,7 @@
         <v>1829</v>
       </c>
       <c r="Q385" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E385))</f>
         <v>1</v>
       </c>
       <c r="R385" s="1" t="s">
@@ -31572,7 +31593,7 @@
     </row>
     <row r="386" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I386)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B386" s="1" t="s">
@@ -31585,7 +31606,7 @@
         <v>621</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>54</v>
@@ -31615,14 +31636,14 @@
         <v>1829</v>
       </c>
       <c r="Q386" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E386))</f>
         <v>1</v>
       </c>
       <c r="R386" s="1" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="S386" s="1" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="T386" s="1">
         <v>0</v>
@@ -31630,7 +31651,7 @@
     </row>
     <row r="387" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I387)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B387" s="1" t="s">
@@ -31673,7 +31694,7 @@
         <v>1829</v>
       </c>
       <c r="Q387" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E387))</f>
         <v>0</v>
       </c>
       <c r="R387" s="1" t="s">
@@ -31688,7 +31709,7 @@
     </row>
     <row r="388" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I388)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B388" s="1" t="s">
@@ -31731,7 +31752,7 @@
         <v>1829</v>
       </c>
       <c r="Q388" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E388))</f>
         <v>0</v>
       </c>
       <c r="R388" s="1" t="s">
@@ -31746,7 +31767,7 @@
     </row>
     <row r="389" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I389)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B389" s="1" t="s">
@@ -31765,7 +31786,7 @@
         <v>53</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
@@ -31789,14 +31810,14 @@
         <v>1829</v>
       </c>
       <c r="Q389" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E389))</f>
         <v>0</v>
       </c>
       <c r="R389" s="1" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="S389" s="1" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="T389" s="1">
         <v>2</v>
@@ -31804,7 +31825,7 @@
     </row>
     <row r="390" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I390)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B390" s="1" t="s">
@@ -31845,7 +31866,7 @@
         <v>1829</v>
       </c>
       <c r="Q390" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E390))</f>
         <v>0</v>
       </c>
       <c r="R390" s="1" t="s">
@@ -31860,7 +31881,7 @@
     </row>
     <row r="391" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I391)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B391" s="1" t="s">
@@ -31901,7 +31922,7 @@
         <v>1829</v>
       </c>
       <c r="Q391" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E391))</f>
         <v>0</v>
       </c>
       <c r="R391" s="1" t="s">
@@ -31916,7 +31937,7 @@
     </row>
     <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I392)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B392" s="1" t="s">
@@ -31936,7 +31957,7 @@
       </c>
       <c r="G392" s="1"/>
       <c r="H392" s="1" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -31959,7 +31980,7 @@
         <v>1829</v>
       </c>
       <c r="Q392" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E392))</f>
         <v>0</v>
       </c>
       <c r="R392" s="1" t="s">
@@ -31974,7 +31995,7 @@
     </row>
     <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I393)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B393" s="1" t="s">
@@ -32017,7 +32038,7 @@
         <v>1829</v>
       </c>
       <c r="Q393" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E393))</f>
         <v>0</v>
       </c>
       <c r="R393" s="1" t="s">
@@ -32032,7 +32053,7 @@
     </row>
     <row r="394" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I394)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B394" s="1" t="s">
@@ -32045,7 +32066,7 @@
         <v>621</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F394" s="1" t="s">
         <v>54</v>
@@ -32075,14 +32096,14 @@
         <v>1829</v>
       </c>
       <c r="Q394" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E394))</f>
         <v>1</v>
       </c>
       <c r="R394" s="1" t="s">
         <v>1647</v>
       </c>
       <c r="S394" s="1" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T394" s="1">
         <v>0</v>
@@ -32090,7 +32111,7 @@
     </row>
     <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I395)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B395" s="1" t="s">
@@ -32109,7 +32130,7 @@
         <v>53</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="H395" s="1"/>
       <c r="I395" s="1"/>
@@ -32133,7 +32154,7 @@
         <v>1829</v>
       </c>
       <c r="Q395" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E395))</f>
         <v>0</v>
       </c>
       <c r="R395" s="1" t="s">
@@ -32148,7 +32169,7 @@
     </row>
     <row r="396" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I396)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B396" s="1" t="s">
@@ -32189,7 +32210,7 @@
         <v>1829</v>
       </c>
       <c r="Q396" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E396))</f>
         <v>0</v>
       </c>
       <c r="R396" s="1" t="s">
@@ -32204,7 +32225,7 @@
     </row>
     <row r="397" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I397)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -32217,7 +32238,7 @@
         <v>621</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F397" s="1" t="s">
         <v>54</v>
@@ -32247,14 +32268,14 @@
         <v>1829</v>
       </c>
       <c r="Q397" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E397))</f>
         <v>1</v>
       </c>
       <c r="R397" s="1" t="s">
         <v>1648</v>
       </c>
       <c r="S397" s="1" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="T397" s="1">
         <v>0</v>
@@ -32262,7 +32283,7 @@
     </row>
     <row r="398" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(ISBLANK(I398)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B398" s="1" t="s">
@@ -32282,7 +32303,7 @@
       </c>
       <c r="G398" s="1"/>
       <c r="H398" s="1" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -32305,7 +32326,7 @@
         <v>1829</v>
       </c>
       <c r="Q398" s="1" t="b">
-        <f t="shared" si="15"/>
+        <f>ISNUMBER(SEARCH(",",E398))</f>
         <v>0</v>
       </c>
       <c r="R398" s="1" t="s">
@@ -32320,7 +32341,7 @@
     </row>
     <row r="399" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="str">
-        <f t="shared" ref="A399:A430" si="16">IF(ISBLANK(I399)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I399)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B399" s="1" t="s">
@@ -32363,7 +32384,7 @@
         <v>1829</v>
       </c>
       <c r="Q399" s="1" t="b">
-        <f t="shared" ref="Q399:Q430" si="17">ISNUMBER(SEARCH(",",E399))</f>
+        <f>ISNUMBER(SEARCH(",",E399))</f>
         <v>0</v>
       </c>
       <c r="R399" s="1" t="s">
@@ -32378,7 +32399,7 @@
     </row>
     <row r="400" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I400)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B400" s="1" t="s">
@@ -32391,7 +32412,7 @@
         <v>650</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>54</v>
@@ -32419,7 +32440,7 @@
         <v>1829</v>
       </c>
       <c r="Q400" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E400))</f>
         <v>1</v>
       </c>
       <c r="R400" s="1" t="s">
@@ -32434,7 +32455,7 @@
     </row>
     <row r="401" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I401)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B401" s="1" t="s">
@@ -32475,14 +32496,14 @@
         <v>1829</v>
       </c>
       <c r="Q401" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E401))</f>
         <v>0</v>
       </c>
       <c r="R401" s="1" t="s">
         <v>1732</v>
       </c>
       <c r="S401" s="1" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="T401" s="1">
         <v>0</v>
@@ -32490,7 +32511,7 @@
     </row>
     <row r="402" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I402)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B402" s="1" t="s">
@@ -32533,7 +32554,7 @@
         <v>1829</v>
       </c>
       <c r="Q402" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E402))</f>
         <v>0</v>
       </c>
       <c r="R402" s="1" t="s">
@@ -32548,7 +32569,7 @@
     </row>
     <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I403)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B403" s="1" t="s">
@@ -32568,7 +32589,7 @@
       </c>
       <c r="G403" s="1"/>
       <c r="H403" s="1" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -32591,7 +32612,7 @@
         <v>1829</v>
       </c>
       <c r="Q403" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E403))</f>
         <v>0</v>
       </c>
       <c r="R403" s="1" t="s">
@@ -32606,7 +32627,7 @@
     </row>
     <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I404)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B404" s="1" t="s">
@@ -32647,7 +32668,7 @@
         <v>1829</v>
       </c>
       <c r="Q404" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E404))</f>
         <v>0</v>
       </c>
       <c r="R404" s="1" t="s">
@@ -32662,7 +32683,7 @@
     </row>
     <row r="405" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I405)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B405" s="1" t="s">
@@ -32681,7 +32702,7 @@
         <v>53</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="H405" s="1"/>
       <c r="I405" s="1"/>
@@ -32705,7 +32726,7 @@
         <v>1829</v>
       </c>
       <c r="Q405" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E405))</f>
         <v>0</v>
       </c>
       <c r="R405" s="1" t="s">
@@ -32720,7 +32741,7 @@
     </row>
     <row r="406" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I406)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B406" s="1" t="s">
@@ -32763,7 +32784,7 @@
         <v>1829</v>
       </c>
       <c r="Q406" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E406))</f>
         <v>0</v>
       </c>
       <c r="R406" s="1" t="s">
@@ -32778,7 +32799,7 @@
     </row>
     <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I407)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B407" s="1" t="s">
@@ -32821,7 +32842,7 @@
         <v>1829</v>
       </c>
       <c r="Q407" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E407))</f>
         <v>1</v>
       </c>
       <c r="R407" s="1" t="s">
@@ -32836,7 +32857,7 @@
     </row>
     <row r="408" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I408)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B408" s="1" t="s">
@@ -32877,14 +32898,14 @@
         <v>1829</v>
       </c>
       <c r="Q408" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E408))</f>
         <v>0</v>
       </c>
       <c r="R408" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="S408" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="T408" s="1">
         <v>0</v>
@@ -32892,7 +32913,7 @@
     </row>
     <row r="409" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I409)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B409" s="1" t="s">
@@ -32933,7 +32954,7 @@
         <v>1829</v>
       </c>
       <c r="Q409" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E409))</f>
         <v>0</v>
       </c>
       <c r="R409" s="1" t="s">
@@ -32948,7 +32969,7 @@
     </row>
     <row r="410" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I410)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B410" s="1" t="s">
@@ -32991,14 +33012,14 @@
         <v>1829</v>
       </c>
       <c r="Q410" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E410))</f>
         <v>1</v>
       </c>
       <c r="R410" s="1" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="S410" s="1" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="T410" s="1">
         <v>0</v>
@@ -33006,7 +33027,7 @@
     </row>
     <row r="411" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I411)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -33049,7 +33070,7 @@
         <v>1829</v>
       </c>
       <c r="Q411" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E411))</f>
         <v>1</v>
       </c>
       <c r="R411" s="1" t="s">
@@ -33064,7 +33085,7 @@
     </row>
     <row r="412" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I412)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -33105,7 +33126,7 @@
         <v>1829</v>
       </c>
       <c r="Q412" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E412))</f>
         <v>1</v>
       </c>
       <c r="R412" s="1" t="s">
@@ -33120,7 +33141,7 @@
     </row>
     <row r="413" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I413)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -33163,7 +33184,7 @@
         <v>1829</v>
       </c>
       <c r="Q413" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E413))</f>
         <v>1</v>
       </c>
       <c r="R413" s="1" t="s">
@@ -33178,7 +33199,7 @@
     </row>
     <row r="414" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I414)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -33221,7 +33242,7 @@
         <v>1829</v>
       </c>
       <c r="Q414" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E414))</f>
         <v>1</v>
       </c>
       <c r="R414" s="1" t="s">
@@ -33236,7 +33257,7 @@
     </row>
     <row r="415" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I415)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -33279,7 +33300,7 @@
         <v>1829</v>
       </c>
       <c r="Q415" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E415))</f>
         <v>1</v>
       </c>
       <c r="R415" s="1" t="s">
@@ -33294,7 +33315,7 @@
     </row>
     <row r="416" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I416)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -33316,7 +33337,7 @@
         <v>961</v>
       </c>
       <c r="H416" s="1" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="I416" s="1"/>
       <c r="J416" s="1"/>
@@ -33339,7 +33360,7 @@
         <v>1829</v>
       </c>
       <c r="Q416" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E416))</f>
         <v>0</v>
       </c>
       <c r="R416" s="1" t="s">
@@ -33354,7 +33375,7 @@
     </row>
     <row r="417" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I417)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -33376,7 +33397,7 @@
         <v>1833</v>
       </c>
       <c r="H417" s="1" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="I417" s="1"/>
       <c r="J417" s="1"/>
@@ -33399,7 +33420,7 @@
         <v>1829</v>
       </c>
       <c r="Q417" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E417))</f>
         <v>1</v>
       </c>
       <c r="R417" s="1" t="s">
@@ -33414,7 +33435,7 @@
     </row>
     <row r="418" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I418)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -33427,7 +33448,7 @@
         <v>621</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F418" s="1" t="s">
         <v>54</v>
@@ -33457,7 +33478,7 @@
         <v>1829</v>
       </c>
       <c r="Q418" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E418))</f>
         <v>1</v>
       </c>
       <c r="R418" s="1" t="s">
@@ -33472,7 +33493,7 @@
     </row>
     <row r="419" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I419)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -33515,7 +33536,7 @@
         <v>1829</v>
       </c>
       <c r="Q419" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E419))</f>
         <v>1</v>
       </c>
       <c r="R419" s="1" t="s">
@@ -33530,7 +33551,7 @@
     </row>
     <row r="420" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I420)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -33573,7 +33594,7 @@
         <v>1829</v>
       </c>
       <c r="Q420" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E420))</f>
         <v>1</v>
       </c>
       <c r="R420" s="1" t="s">
@@ -33588,7 +33609,7 @@
     </row>
     <row r="421" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I421)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -33607,7 +33628,7 @@
         <v>52</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="H421" s="1"/>
       <c r="I421" s="1"/>
@@ -33631,7 +33652,7 @@
         <v>1829</v>
       </c>
       <c r="Q421" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E421))</f>
         <v>1</v>
       </c>
       <c r="R421" s="1" t="s">
@@ -33646,7 +33667,7 @@
     </row>
     <row r="422" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I422)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -33659,7 +33680,7 @@
         <v>621</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>54</v>
@@ -33691,14 +33712,14 @@
         <v>1829</v>
       </c>
       <c r="Q422" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E422))</f>
         <v>1</v>
       </c>
       <c r="R422" s="1" t="s">
         <v>1651</v>
       </c>
       <c r="S422" s="1" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="T422" s="1">
         <v>0</v>
@@ -33706,7 +33727,7 @@
     </row>
     <row r="423" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I423)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -33725,7 +33746,7 @@
         <v>54</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="H423" s="1" t="s">
         <v>1835</v>
@@ -33751,7 +33772,7 @@
         <v>1829</v>
       </c>
       <c r="Q423" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E423))</f>
         <v>1</v>
       </c>
       <c r="R423" s="1" t="s">
@@ -33766,7 +33787,7 @@
     </row>
     <row r="424" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I424)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -33809,7 +33830,7 @@
         <v>1829</v>
       </c>
       <c r="Q424" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E424))</f>
         <v>0</v>
       </c>
       <c r="R424" s="1" t="s">
@@ -33824,7 +33845,7 @@
     </row>
     <row r="425" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I425)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -33865,7 +33886,7 @@
         <v>1829</v>
       </c>
       <c r="Q425" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E425))</f>
         <v>0</v>
       </c>
       <c r="R425" s="1" t="s">
@@ -33880,7 +33901,7 @@
     </row>
     <row r="426" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I426)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -33925,7 +33946,7 @@
         <v>1829</v>
       </c>
       <c r="Q426" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E426))</f>
         <v>1</v>
       </c>
       <c r="R426" s="1" t="s">
@@ -33940,7 +33961,7 @@
     </row>
     <row r="427" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I427)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -33983,7 +34004,7 @@
         <v>1829</v>
       </c>
       <c r="Q427" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E427))</f>
         <v>1</v>
       </c>
       <c r="R427" s="1" t="s">
@@ -33998,7 +34019,7 @@
     </row>
     <row r="428" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I428)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -34043,7 +34064,7 @@
         <v>1829</v>
       </c>
       <c r="Q428" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E428))</f>
         <v>1</v>
       </c>
       <c r="R428" s="1" t="s">
@@ -34058,7 +34079,7 @@
     </row>
     <row r="429" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I429)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -34101,7 +34122,7 @@
         <v>1829</v>
       </c>
       <c r="Q429" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E429))</f>
         <v>1</v>
       </c>
       <c r="R429" s="1" t="s">
@@ -34116,7 +34137,7 @@
     </row>
     <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISBLANK(I430)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -34139,7 +34160,7 @@
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
       <c r="K430" s="1" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="L430" s="1" t="str" cm="1">
         <f t="array" ref="L430">_xlfn.REGEXEXTRACT(B430,"(?&lt;=//)[^/]+")</f>
@@ -34159,14 +34180,14 @@
         <v>1829</v>
       </c>
       <c r="Q430" s="1" t="b">
-        <f t="shared" si="17"/>
+        <f>ISNUMBER(SEARCH(",",E430))</f>
         <v>0</v>
       </c>
       <c r="R430" s="1" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="S430" s="1" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="T430" s="1">
         <v>0</v>
@@ -34174,7 +34195,7 @@
     </row>
     <row r="431" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="str">
-        <f t="shared" ref="A431:A459" si="18">IF(ISBLANK(I431)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I431)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -34187,7 +34208,7 @@
         <v>650</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="F431" s="1" t="s">
         <v>54</v>
@@ -34217,7 +34238,7 @@
         <v>1829</v>
       </c>
       <c r="Q431" s="1" t="b">
-        <f t="shared" ref="Q431:Q459" si="19">ISNUMBER(SEARCH(",",E431))</f>
+        <f>ISNUMBER(SEARCH(",",E431))</f>
         <v>1</v>
       </c>
       <c r="R431" s="1" t="s">
@@ -34232,7 +34253,7 @@
     </row>
     <row r="432" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I432)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -34277,7 +34298,7 @@
         <v>1829</v>
       </c>
       <c r="Q432" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E432))</f>
         <v>1</v>
       </c>
       <c r="R432" s="1" t="s">
@@ -34292,7 +34313,7 @@
     </row>
     <row r="433" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I433)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -34335,7 +34356,7 @@
         <v>1829</v>
       </c>
       <c r="Q433" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E433))</f>
         <v>1</v>
       </c>
       <c r="R433" s="1" t="s">
@@ -34350,7 +34371,7 @@
     </row>
     <row r="434" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I434)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -34363,7 +34384,7 @@
         <v>627</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>53</v>
@@ -34393,14 +34414,14 @@
         <v>1829</v>
       </c>
       <c r="Q434" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E434))</f>
         <v>1</v>
       </c>
       <c r="R434" s="1" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="S434" s="1" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="T434" s="1">
         <v>1</v>
@@ -34408,7 +34429,7 @@
     </row>
     <row r="435" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I435)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -34449,7 +34470,7 @@
         <v>1829</v>
       </c>
       <c r="Q435" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E435))</f>
         <v>0</v>
       </c>
       <c r="R435" s="1" t="s">
@@ -34464,7 +34485,7 @@
     </row>
     <row r="436" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I436)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -34507,7 +34528,7 @@
         <v>1829</v>
       </c>
       <c r="Q436" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E436))</f>
         <v>1</v>
       </c>
       <c r="R436" s="1" t="s">
@@ -34522,7 +34543,7 @@
     </row>
     <row r="437" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I437)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -34565,7 +34586,7 @@
         <v>1829</v>
       </c>
       <c r="Q437" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E437))</f>
         <v>1</v>
       </c>
       <c r="R437" s="1" t="s">
@@ -34580,7 +34601,7 @@
     </row>
     <row r="438" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I438)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -34599,7 +34620,7 @@
         <v>53</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -34623,7 +34644,7 @@
         <v>1829</v>
       </c>
       <c r="Q438" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E438))</f>
         <v>1</v>
       </c>
       <c r="R438" s="1" t="s">
@@ -34638,7 +34659,7 @@
     </row>
     <row r="439" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I439)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -34679,7 +34700,7 @@
         <v>1829</v>
       </c>
       <c r="Q439" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E439))</f>
         <v>0</v>
       </c>
       <c r="R439" s="1" t="s">
@@ -34694,7 +34715,7 @@
     </row>
     <row r="440" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I440)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -34737,14 +34758,14 @@
         <v>1829</v>
       </c>
       <c r="Q440" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E440))</f>
         <v>1</v>
       </c>
       <c r="R440" s="1" t="s">
         <v>1655</v>
       </c>
       <c r="S440" s="1" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="T440" s="1">
         <v>0</v>
@@ -34752,11 +34773,11 @@
     </row>
     <row r="441" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I441)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C441" s="1">
         <v>81</v>
@@ -34795,7 +34816,7 @@
         <v>1829</v>
       </c>
       <c r="Q441" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E441))</f>
         <v>1</v>
       </c>
       <c r="R441" s="1" t="s">
@@ -34810,7 +34831,7 @@
     </row>
     <row r="442" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I442)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -34853,7 +34874,7 @@
         <v>1829</v>
       </c>
       <c r="Q442" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E442))</f>
         <v>1</v>
       </c>
       <c r="R442" s="1" t="s">
@@ -34868,7 +34889,7 @@
     </row>
     <row r="443" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I443)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -34881,7 +34902,7 @@
         <v>627</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>54</v>
@@ -34911,11 +34932,11 @@
         <v>1829</v>
       </c>
       <c r="Q443" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E443))</f>
         <v>1</v>
       </c>
       <c r="R443" s="1" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="S443" s="1" t="s">
         <v>1606</v>
@@ -34926,7 +34947,7 @@
     </row>
     <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I444)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -34967,7 +34988,7 @@
         <v>1829</v>
       </c>
       <c r="Q444" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E444))</f>
         <v>1</v>
       </c>
       <c r="R444" s="1" t="s">
@@ -34982,7 +35003,7 @@
     </row>
     <row r="445" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I445)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -35027,7 +35048,7 @@
         <v>1829</v>
       </c>
       <c r="Q445" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E445))</f>
         <v>1</v>
       </c>
       <c r="R445" s="1" t="s">
@@ -35042,7 +35063,7 @@
     </row>
     <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I446)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -35085,7 +35106,7 @@
         <v>1829</v>
       </c>
       <c r="Q446" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E446))</f>
         <v>1</v>
       </c>
       <c r="R446" s="1" t="s">
@@ -35100,7 +35121,7 @@
     </row>
     <row r="447" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I447)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -35145,7 +35166,7 @@
         <v>1829</v>
       </c>
       <c r="Q447" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E447))</f>
         <v>1</v>
       </c>
       <c r="R447" s="1" t="s">
@@ -35160,7 +35181,7 @@
     </row>
     <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I448)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -35203,7 +35224,7 @@
         <v>1829</v>
       </c>
       <c r="Q448" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E448))</f>
         <v>1</v>
       </c>
       <c r="R448" s="1" t="s">
@@ -35218,7 +35239,7 @@
     </row>
     <row r="449" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I449)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -35261,7 +35282,7 @@
         <v>1829</v>
       </c>
       <c r="Q449" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E449))</f>
         <v>0</v>
       </c>
       <c r="R449" s="1" t="s">
@@ -35276,7 +35297,7 @@
     </row>
     <row r="450" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I450)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -35319,7 +35340,7 @@
         <v>1829</v>
       </c>
       <c r="Q450" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E450))</f>
         <v>0</v>
       </c>
       <c r="R450" s="1" t="s">
@@ -35334,7 +35355,7 @@
     </row>
     <row r="451" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I451)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -35347,7 +35368,7 @@
         <v>625</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="F451" s="1" t="s">
         <v>54</v>
@@ -35379,7 +35400,7 @@
         <v>1829</v>
       </c>
       <c r="Q451" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E451))</f>
         <v>1</v>
       </c>
       <c r="R451" s="1" t="s">
@@ -35394,7 +35415,7 @@
     </row>
     <row r="452" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I452)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -35439,7 +35460,7 @@
         <v>1829</v>
       </c>
       <c r="Q452" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E452))</f>
         <v>1</v>
       </c>
       <c r="R452" s="1" t="s">
@@ -35454,7 +35475,7 @@
     </row>
     <row r="453" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I453)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -35497,7 +35518,7 @@
         <v>1829</v>
       </c>
       <c r="Q453" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E453))</f>
         <v>0</v>
       </c>
       <c r="R453" s="1" t="s">
@@ -35512,7 +35533,7 @@
     </row>
     <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I454)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -35555,7 +35576,7 @@
         <v>1829</v>
       </c>
       <c r="Q454" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E454))</f>
         <v>1</v>
       </c>
       <c r="R454" s="1" t="s">
@@ -35570,7 +35591,7 @@
     </row>
     <row r="455" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I455)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B455" s="1" t="s">
@@ -35613,14 +35634,14 @@
         <v>1829</v>
       </c>
       <c r="Q455" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E455))</f>
         <v>1</v>
       </c>
       <c r="R455" s="1" t="s">
         <v>1656</v>
       </c>
       <c r="S455" s="1" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="T455" s="1">
         <v>0</v>
@@ -35628,7 +35649,7 @@
     </row>
     <row r="456" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I456)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B456" s="1" t="s">
@@ -35641,13 +35662,13 @@
         <v>761</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H456" s="1"/>
       <c r="I456" s="1"/>
@@ -35671,7 +35692,7 @@
         <v>1829</v>
       </c>
       <c r="Q456" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E456))</f>
         <v>1</v>
       </c>
       <c r="R456" s="1" t="s">
@@ -35686,7 +35707,7 @@
     </row>
     <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I457)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B457" s="1" t="s">
@@ -35729,7 +35750,7 @@
         <v>1829</v>
       </c>
       <c r="Q457" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E457))</f>
         <v>1</v>
       </c>
       <c r="R457" s="1" t="s">
@@ -35744,7 +35765,7 @@
     </row>
     <row r="458" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I458)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B458" s="1" t="s">
@@ -35789,7 +35810,7 @@
         <v>1829</v>
       </c>
       <c r="Q458" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E458))</f>
         <v>1</v>
       </c>
       <c r="R458" s="1" t="s">
@@ -35804,7 +35825,7 @@
     </row>
     <row r="459" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(ISBLANK(I459)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -35847,7 +35868,7 @@
         <v>1829</v>
       </c>
       <c r="Q459" s="1" t="b">
-        <f t="shared" si="19"/>
+        <f>ISNUMBER(SEARCH(",",E459))</f>
         <v>1</v>
       </c>
       <c r="R459" s="1" t="s">
@@ -35862,7 +35883,7 @@
     </row>
     <row r="460" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="str">
-        <f t="shared" ref="A460:A466" si="20">IF(ISBLANK(I460)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A460:A466" si="10">IF(ISBLANK(I460)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -35905,7 +35926,7 @@
         <v>1829</v>
       </c>
       <c r="Q460" s="1" t="b">
-        <f t="shared" ref="Q460:Q466" si="21">ISNUMBER(SEARCH(",",E460))</f>
+        <f t="shared" ref="Q460:Q466" si="11">ISNUMBER(SEARCH(",",E460))</f>
         <v>1</v>
       </c>
       <c r="R460" s="1" t="s">
@@ -35920,7 +35941,7 @@
     </row>
     <row r="461" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -35963,7 +35984,7 @@
         <v>1829</v>
       </c>
       <c r="Q461" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R461" s="1" t="s">
@@ -35978,7 +35999,7 @@
     </row>
     <row r="462" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -36023,7 +36044,7 @@
         <v>1829</v>
       </c>
       <c r="Q462" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R462" s="1" t="s">
@@ -36038,7 +36059,7 @@
     </row>
     <row r="463" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -36079,7 +36100,7 @@
         <v>1829</v>
       </c>
       <c r="Q463" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R463" s="1" t="s">
@@ -36094,7 +36115,7 @@
     </row>
     <row r="464" spans="1:20" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -36137,7 +36158,7 @@
         <v>1829</v>
       </c>
       <c r="Q464" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R464" s="1" t="s">
@@ -36152,7 +36173,7 @@
     </row>
     <row r="465" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -36177,7 +36198,7 @@
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
       <c r="K465" s="1" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="L465" s="1" t="str" cm="1">
         <f t="array" ref="L465">_xlfn.REGEXEXTRACT(B465,"(?&lt;=//)[^/]+")</f>
@@ -36197,7 +36218,7 @@
         <v>1829</v>
       </c>
       <c r="Q465" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R465" s="1" t="s">
@@ -36212,7 +36233,7 @@
     </row>
     <row r="466" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -36225,7 +36246,7 @@
         <v>844</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>54</v>
@@ -36255,7 +36276,7 @@
         <v>1829</v>
       </c>
       <c r="Q466" s="1" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R466" s="1" t="s">
